--- a/AAII_Financials/Quarterly/OBLG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OBLG_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
   <si>
     <t>OBLG</t>
   </si>
@@ -1342,8 +1342,8 @@
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>17</v>
+      <c r="D17" s="3">
+        <v>1800</v>
       </c>
       <c r="E17" s="3">
         <v>2000</v>
@@ -1416,8 +1416,8 @@
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>17</v>
+      <c r="D18" s="3">
+        <v>-900</v>
       </c>
       <c r="E18" s="3">
         <v>-1000</v>
@@ -1518,8 +1518,8 @@
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>17</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1592,8 +1592,8 @@
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>17</v>
+      <c r="D21" s="3">
+        <v>-800</v>
       </c>
       <c r="E21" s="3">
         <v>-1000</v>
@@ -1962,8 +1962,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>17</v>
+      <c r="D26" s="3">
+        <v>-900</v>
       </c>
       <c r="E26" s="3">
         <v>-1000</v>
@@ -2036,8 +2036,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>17</v>
+      <c r="D27" s="3">
+        <v>-1000</v>
       </c>
       <c r="E27" s="3">
         <v>-1900</v>
@@ -2406,8 +2406,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>17</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -2480,8 +2480,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>17</v>
+      <c r="D33" s="3">
+        <v>-1000</v>
       </c>
       <c r="E33" s="3">
         <v>-1900</v>
@@ -2628,8 +2628,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>17</v>
+      <c r="D35" s="3">
+        <v>-1000</v>
       </c>
       <c r="E35" s="3">
         <v>-1900</v>
@@ -4994,7 +4994,7 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>227000</v>
+        <v>-227000</v>
       </c>
       <c r="E72" s="3">
         <v>-226100</v>
@@ -5516,8 +5516,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>17</v>
+      <c r="D81" s="3">
+        <v>-1000</v>
       </c>
       <c r="E81" s="3">
         <v>-1900</v>
@@ -6063,7 +6063,7 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4500</v>
+        <v>-100</v>
       </c>
       <c r="E89" s="3">
         <v>-1300</v>
@@ -6933,7 +6933,7 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-7500</v>
+        <v>-100</v>
       </c>
       <c r="E102" s="3">
         <v>3200</v>

--- a/AAII_Financials/Quarterly/OBLG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OBLG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
   <si>
     <t>OBLG</t>
   </si>
@@ -656,192 +656,205 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>600</v>
+      </c>
+      <c r="E8" s="3">
         <v>900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
+        <v>900</v>
+      </c>
+      <c r="G8" s="3">
         <v>1000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1500</v>
-      </c>
-      <c r="K8" s="3">
-        <v>2000</v>
-      </c>
-      <c r="L8" s="3">
-        <v>1800</v>
       </c>
       <c r="M8" s="3">
         <v>2000</v>
       </c>
       <c r="N8" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O8" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P8" s="3">
         <v>1900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>3900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>3300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>8100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>5300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>5400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>2400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>2400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>2600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>2900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>2900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>3300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -849,147 +862,159 @@
         <v>600</v>
       </c>
       <c r="E9" s="3">
+        <v>700</v>
+      </c>
+      <c r="F9" s="3">
+        <v>600</v>
+      </c>
+      <c r="G9" s="3">
         <v>800</v>
-      </c>
-      <c r="F9" s="3">
-        <v>800</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1100</v>
       </c>
       <c r="H9" s="3">
         <v>800</v>
       </c>
       <c r="I9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J9" s="3">
+        <v>800</v>
+      </c>
+      <c r="K9" s="3">
         <v>900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>1300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>1600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>4100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>2400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>2500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>1600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>1700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>1800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>1900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E10" s="3">
         <v>200</v>
       </c>
       <c r="F10" s="3">
+        <v>300</v>
+      </c>
+      <c r="G10" s="3">
         <v>200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>200</v>
+      </c>
+      <c r="I10" s="3">
         <v>300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>700</v>
-      </c>
-      <c r="L10" s="3">
-        <v>600</v>
-      </c>
-      <c r="M10" s="3">
-        <v>800</v>
       </c>
       <c r="N10" s="3">
         <v>600</v>
       </c>
       <c r="O10" s="3">
+        <v>800</v>
+      </c>
+      <c r="P10" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q10" s="3">
         <v>2300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>4000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>2900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>2900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>1200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>1100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>1400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1016,13 +1041,15 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12" s="3">
         <v>0</v>
@@ -1031,25 +1058,25 @@
         <v>0</v>
       </c>
       <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
         <v>100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>1000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>900</v>
-      </c>
-      <c r="L12" s="3">
-        <v>700</v>
-      </c>
-      <c r="M12" s="3">
-        <v>600</v>
       </c>
       <c r="N12" s="3">
         <v>700</v>
@@ -1061,19 +1088,19 @@
         <v>700</v>
       </c>
       <c r="Q12" s="3">
+        <v>600</v>
+      </c>
+      <c r="R12" s="3">
+        <v>700</v>
+      </c>
+      <c r="S12" s="3">
         <v>2300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>1300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>1400</v>
-      </c>
-      <c r="T12" s="3">
-        <v>200</v>
-      </c>
-      <c r="U12" s="3">
-        <v>200</v>
       </c>
       <c r="V12" s="3">
         <v>200</v>
@@ -1088,10 +1115,16 @@
         <v>200</v>
       </c>
       <c r="Z12" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB12" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1164,87 +1197,99 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E14" s="3">
+        <v>300</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>-400</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>5200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>6900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>1100</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-2200</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-2600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>1800</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>500</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>1800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>1000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>1500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
         <v>100</v>
@@ -1256,10 +1301,10 @@
         <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
         <v>600</v>
@@ -1268,10 +1313,10 @@
         <v>600</v>
       </c>
       <c r="L15" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="M15" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="N15" s="3">
         <v>700</v>
@@ -1280,25 +1325,25 @@
         <v>700</v>
       </c>
       <c r="P15" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="Q15" s="3">
-        <v>1600</v>
+        <v>700</v>
       </c>
       <c r="R15" s="3">
         <v>800</v>
       </c>
       <c r="S15" s="3">
+        <v>1600</v>
+      </c>
+      <c r="T15" s="3">
+        <v>800</v>
+      </c>
+      <c r="U15" s="3">
         <v>900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>100</v>
-      </c>
-      <c r="U15" s="3">
-        <v>200</v>
-      </c>
-      <c r="V15" s="3">
-        <v>200</v>
       </c>
       <c r="W15" s="3">
         <v>200</v>
@@ -1312,8 +1357,14 @@
       <c r="Z15" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,8 +1388,10 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
@@ -1346,147 +1399,159 @@
         <v>1800</v>
       </c>
       <c r="E17" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G17" s="3">
         <v>2000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>2700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>8300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>10400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>6100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>4500</v>
-      </c>
-      <c r="N17" s="3">
-        <v>5300</v>
-      </c>
-      <c r="O17" s="3">
-        <v>2600</v>
       </c>
       <c r="P17" s="3">
         <v>5300</v>
       </c>
       <c r="Q17" s="3">
+        <v>2600</v>
+      </c>
+      <c r="R17" s="3">
+        <v>5300</v>
+      </c>
+      <c r="S17" s="3">
         <v>14400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>8300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>10900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>3000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>3300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>3200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>5400</v>
-      </c>
-      <c r="X17" s="3">
-        <v>4400</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>5000</v>
       </c>
       <c r="Z17" s="3">
         <v>4400</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AB17" s="3">
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-7100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-9100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-4600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-2800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-2500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-3400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>1300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-6300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-3000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-5500</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-600</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-900</v>
       </c>
       <c r="V18" s="3">
         <v>-600</v>
       </c>
       <c r="W18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="X18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-2500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1513,29 +1578,31 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
@@ -1546,14 +1613,14 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1564,105 +1631,117 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-200</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F21" s="3">
         <v>-800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-1000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-1100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-1100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-6600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-8400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-3900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-2200</v>
       </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3">
         <v>-1500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-2700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>2100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-1200</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-2200</v>
       </c>
       <c r="S21" s="3">
         <v>-4700</v>
       </c>
       <c r="T21" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="U21" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="V21" s="3">
         <v>-500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-2600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1678,15 +1757,15 @@
       <c r="G22" s="3">
         <v>0</v>
       </c>
-      <c r="H22" s="3" t="s">
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
@@ -1703,114 +1782,126 @@
         <v>0</v>
       </c>
       <c r="P22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R22" s="3">
         <v>100</v>
       </c>
       <c r="S22" s="3">
+        <v>200</v>
+      </c>
+      <c r="T22" s="3">
         <v>100</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
       <c r="U22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
       </c>
-      <c r="W22" s="3" t="s">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
       <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-7200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-9000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-4500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-2800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-2200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-3400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>1300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-6500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-3100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-5600</v>
-      </c>
-      <c r="T23" s="3">
-        <v>-600</v>
-      </c>
-      <c r="U23" s="3">
-        <v>-900</v>
       </c>
       <c r="V23" s="3">
         <v>-600</v>
       </c>
       <c r="W23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="X23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Y23" s="3">
         <v>-2700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1836,25 +1927,25 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>100</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>17</v>
@@ -1871,11 +1962,11 @@
       <c r="V24" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
-      <c r="X24" s="3">
-        <v>0</v>
+      <c r="W24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="Y24" s="3">
         <v>0</v>
@@ -1883,8 +1974,14 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2054,174 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-7200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-9000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-4500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-2700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-2200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-3400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>1200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-6500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-3100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-5600</v>
-      </c>
-      <c r="T26" s="3">
-        <v>-600</v>
-      </c>
-      <c r="U26" s="3">
-        <v>-900</v>
       </c>
       <c r="V26" s="3">
         <v>-600</v>
       </c>
       <c r="W26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="X26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-2700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-7200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-9000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-4500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-2700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-2200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-4100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-6500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-3100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-5700</v>
-      </c>
-      <c r="T27" s="3">
-        <v>-600</v>
-      </c>
-      <c r="U27" s="3">
-        <v>-900</v>
       </c>
       <c r="V27" s="3">
         <v>-600</v>
       </c>
       <c r="W27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="X27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-2700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2294,14 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2253,8 +2374,14 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2454,14 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,29 +2534,35 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
@@ -2434,14 +2573,14 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2452,105 +2591,117 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>200</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-7200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-9000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-4500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-2700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-2200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-4100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-6500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-3100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-5700</v>
-      </c>
-      <c r="T33" s="3">
-        <v>-600</v>
-      </c>
-      <c r="U33" s="3">
-        <v>-900</v>
       </c>
       <c r="V33" s="3">
         <v>-600</v>
       </c>
       <c r="W33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="X33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-2700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2774,179 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-7200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-9000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-4500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-2700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-2200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-4100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-6500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-3100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-5700</v>
-      </c>
-      <c r="T35" s="3">
-        <v>-600</v>
-      </c>
-      <c r="U35" s="3">
-        <v>-900</v>
       </c>
       <c r="V35" s="3">
         <v>-600</v>
       </c>
       <c r="W35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="X35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-2700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2973,10 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,82 +3003,90 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F41" s="3">
         <v>6800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>6900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>3700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>3100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>4100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>5100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>6500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>8900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>10700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>13000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>4000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>5100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>2700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>4100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>2100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>4600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>2000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>2600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>2700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2980,138 +3159,150 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
+        <v>400</v>
+      </c>
+      <c r="F43" s="3">
         <v>200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>200</v>
-      </c>
-      <c r="F43" s="3">
-        <v>400</v>
-      </c>
-      <c r="G43" s="3">
-        <v>400</v>
       </c>
       <c r="H43" s="3">
         <v>400</v>
       </c>
       <c r="I43" s="3">
+        <v>400</v>
+      </c>
+      <c r="J43" s="3">
+        <v>400</v>
+      </c>
+      <c r="K43" s="3">
         <v>500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>3200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>2200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>4200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>2500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1500</v>
-      </c>
-      <c r="V43" s="3">
-        <v>1400</v>
-      </c>
-      <c r="W43" s="3">
-        <v>1400</v>
       </c>
       <c r="X43" s="3">
         <v>1400</v>
       </c>
       <c r="Y43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Z43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AA43" s="3">
         <v>1500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>200</v>
+      </c>
+      <c r="F44" s="3">
         <v>300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>2100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>1100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>1300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>1400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>1800</v>
-      </c>
-      <c r="T44" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="U44" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="V44" s="3" t="s">
         <v>17</v>
@@ -3128,156 +3319,174 @@
       <c r="Z44" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB44" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>200</v>
+      </c>
+      <c r="F45" s="3">
         <v>300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>800</v>
-      </c>
-      <c r="F45" s="3">
-        <v>900</v>
-      </c>
-      <c r="G45" s="3">
-        <v>600</v>
       </c>
       <c r="H45" s="3">
         <v>900</v>
       </c>
       <c r="I45" s="3">
+        <v>600</v>
+      </c>
+      <c r="J45" s="3">
+        <v>900</v>
+      </c>
+      <c r="K45" s="3">
         <v>1200</v>
-      </c>
-      <c r="J45" s="3">
-        <v>1500</v>
-      </c>
-      <c r="K45" s="3">
-        <v>1100</v>
       </c>
       <c r="L45" s="3">
         <v>1500</v>
       </c>
       <c r="M45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N45" s="3">
         <v>1500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P45" s="3">
         <v>1200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>1000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>400</v>
-      </c>
-      <c r="U45" s="3">
-        <v>500</v>
-      </c>
-      <c r="V45" s="3">
-        <v>600</v>
       </c>
       <c r="W45" s="3">
         <v>500</v>
       </c>
       <c r="X45" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="Y45" s="3">
         <v>500</v>
       </c>
       <c r="Z45" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA45" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB45" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F46" s="3">
         <v>7600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>8400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>5700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>4900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>6400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>7800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>10300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>12800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>15400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>17600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>8400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>10000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>6700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>7800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>8800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>9900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>2700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>2900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>3700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>3900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>4400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>4700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3350,8 +3559,14 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3359,147 +3574,159 @@
         <v>0</v>
       </c>
       <c r="E48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3">
         <v>100</v>
       </c>
       <c r="H48" s="3">
+        <v>100</v>
+      </c>
+      <c r="I48" s="3">
+        <v>100</v>
+      </c>
+      <c r="J48" s="3">
         <v>200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>300</v>
-      </c>
-      <c r="J48" s="3">
-        <v>700</v>
-      </c>
-      <c r="K48" s="3">
-        <v>800</v>
       </c>
       <c r="L48" s="3">
         <v>700</v>
       </c>
       <c r="M48" s="3">
+        <v>800</v>
+      </c>
+      <c r="N48" s="3">
+        <v>700</v>
+      </c>
+      <c r="O48" s="3">
         <v>1000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>2700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>3700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>4400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>700</v>
-      </c>
-      <c r="X48" s="3">
-        <v>1000</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>1000</v>
       </c>
       <c r="Z48" s="3">
         <v>1000</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AB48" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>6400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>13200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>14900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>15500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>16300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>16900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>17500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>18100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>18700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>19300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>20500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>2700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>2800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>3300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>3300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>5100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>6100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3799,14 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,8 +3879,14 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3664,7 +3903,7 @@
         <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I52" s="3">
         <v>0</v>
@@ -3673,7 +3912,7 @@
         <v>100</v>
       </c>
       <c r="K52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L52" s="3">
         <v>100</v>
@@ -3685,13 +3924,13 @@
         <v>100</v>
       </c>
       <c r="O52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P52" s="3">
         <v>100</v>
       </c>
       <c r="Q52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R52" s="3">
         <v>100</v>
@@ -3700,19 +3939,19 @@
         <v>100</v>
       </c>
       <c r="T52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U52" s="3">
         <v>100</v>
       </c>
       <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3">
         <v>100</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
-      </c>
       <c r="X52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y52" s="3">
         <v>0</v>
@@ -3720,8 +3959,14 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,82 +4039,94 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F54" s="3">
         <v>8000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>8900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>6300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>5700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>7400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>14600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>24200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>28600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>31700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>34900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>26700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>29100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>27200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>29300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>32000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>34900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>5900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>6300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>7600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>8000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>10500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>11900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>13800</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4153,10 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,82 +4183,90 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>200</v>
+      </c>
+      <c r="F57" s="3">
         <v>100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>400</v>
-      </c>
-      <c r="I57" s="3">
-        <v>300</v>
-      </c>
-      <c r="J57" s="3">
-        <v>600</v>
       </c>
       <c r="K57" s="3">
         <v>300</v>
       </c>
       <c r="L57" s="3">
+        <v>600</v>
+      </c>
+      <c r="M57" s="3">
+        <v>300</v>
+      </c>
+      <c r="N57" s="3">
         <v>500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>700</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>600</v>
-      </c>
-      <c r="R57" s="3">
-        <v>900</v>
       </c>
       <c r="S57" s="3">
         <v>600</v>
       </c>
       <c r="T57" s="3">
+        <v>900</v>
+      </c>
+      <c r="U57" s="3">
+        <v>600</v>
+      </c>
+      <c r="V57" s="3">
         <v>400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4034,37 +4301,37 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>2400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>2000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>4900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>3700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>3600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>2700</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="U58" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="X58" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
@@ -4072,156 +4339,174 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E59" s="3">
         <v>1200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G59" s="3">
         <v>1100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>3000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>3300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>3200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>4400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>4200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>5200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>4900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F60" s="3">
         <v>1300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1200</v>
-      </c>
-      <c r="F60" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G60" s="3">
-        <v>1900</v>
       </c>
       <c r="H60" s="3">
         <v>2400</v>
       </c>
       <c r="I60" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J60" s="3">
         <v>2400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="L60" s="3">
         <v>2800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>3000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>3600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>6800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>5600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>10000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>8500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>9700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>8300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4253,32 +4538,32 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>2400</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>3000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>4300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>2000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>2800</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4294,8 +4579,14 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4303,55 +4594,55 @@
         <v>0</v>
       </c>
       <c r="E62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G62" s="3">
         <v>100</v>
       </c>
       <c r="H62" s="3">
+        <v>100</v>
+      </c>
+      <c r="I62" s="3">
+        <v>100</v>
+      </c>
+      <c r="J62" s="3">
         <v>200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>500</v>
-      </c>
-      <c r="K62" s="3">
-        <v>600</v>
-      </c>
-      <c r="L62" s="3">
-        <v>600</v>
       </c>
       <c r="M62" s="3">
         <v>600</v>
       </c>
       <c r="N62" s="3">
+        <v>600</v>
+      </c>
+      <c r="O62" s="3">
+        <v>600</v>
+      </c>
+      <c r="P62" s="3">
         <v>1000</v>
-      </c>
-      <c r="O62" s="3">
-        <v>1100</v>
-      </c>
-      <c r="P62" s="3">
-        <v>900</v>
       </c>
       <c r="Q62" s="3">
         <v>1100</v>
       </c>
       <c r="R62" s="3">
+        <v>900</v>
+      </c>
+      <c r="S62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="T62" s="3">
         <v>1500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>2000</v>
-      </c>
-      <c r="T62" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="U62" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>17</v>
@@ -4368,8 +4659,14 @@
       <c r="Z62" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB62" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4739,14 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4819,14 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,82 +4899,94 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F66" s="3">
         <v>1300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>2600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>2600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>3300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>3100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>3600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>6600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>7700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>7100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>13900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>13900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>13200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>13100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +5013,10 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +5089,14 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5169,14 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4914,8 +5249,14 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,82 +5329,94 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-229400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-228200</v>
+      </c>
+      <c r="F72" s="3">
         <v>-227000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-226100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-225100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-223800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-222600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-215500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-206400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-201900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-199200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-198500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-196300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-192900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-194000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-191900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-188600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-185400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-179800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-179100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-178300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-177700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-174900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-173500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-171800</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5489,14 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5569,14 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,82 +5649,94 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F76" s="3">
         <v>6700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>7600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>3900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>3600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>4800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>11900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>20900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>25500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>28100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>28300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>18900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>22100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>13300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>15400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>18800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>21800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>4700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>5400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>6200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>6800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>9500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>10900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5809,179 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-7200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-9000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-4500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-2700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-2200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-4100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-6500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-3100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-5700</v>
-      </c>
-      <c r="T81" s="3">
-        <v>-600</v>
-      </c>
-      <c r="U81" s="3">
-        <v>-900</v>
       </c>
       <c r="V81" s="3">
         <v>-600</v>
       </c>
       <c r="W81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="X81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-2700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,13 +6008,15 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
         <v>100</v>
@@ -5631,10 +6028,10 @@
         <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="J83" s="3">
         <v>600</v>
@@ -5643,10 +6040,10 @@
         <v>600</v>
       </c>
       <c r="L83" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="M83" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="N83" s="3">
         <v>700</v>
@@ -5655,25 +6052,25 @@
         <v>700</v>
       </c>
       <c r="P83" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="Q83" s="3">
-        <v>1600</v>
+        <v>700</v>
       </c>
       <c r="R83" s="3">
         <v>800</v>
       </c>
       <c r="S83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="T83" s="3">
+        <v>800</v>
+      </c>
+      <c r="U83" s="3">
         <v>900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>100</v>
-      </c>
-      <c r="U83" s="3">
-        <v>200</v>
-      </c>
-      <c r="V83" s="3">
-        <v>200</v>
       </c>
       <c r="W83" s="3">
         <v>200</v>
@@ -5687,8 +6084,14 @@
       <c r="Z83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +6164,14 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6244,14 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6324,14 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6404,14 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,82 +6484,94 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F89" s="3">
         <v>-100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-2400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-2300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-2400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-1200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-2200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-2900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-2500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-2600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,8 +6598,10 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6206,15 +6647,15 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
@@ -6225,16 +6666,22 @@
         <v>0</v>
       </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-200</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6754,14 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,13 +6834,19 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
@@ -6432,14 +6891,14 @@
         <v>0</v>
       </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>2200</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
@@ -6447,16 +6906,22 @@
         <v>0</v>
       </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-200</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,8 +6948,10 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6557,8 +7024,14 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +7104,14 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +7184,14 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,8 +7264,14 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6788,56 +7279,56 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>4500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>1500</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3" t="s">
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J100" s="3" t="s">
+      <c r="L100" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>11500</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>4900</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>2400</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>3800</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
@@ -6845,16 +7336,22 @@
         <v>0</v>
       </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-100</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6927,78 +7424,90 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>3200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-1000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-1500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-2400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-1800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-2300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>9100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-1300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>2600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-2500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>3300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>300</v>
-      </c>
-      <c r="U102" s="3">
-        <v>-600</v>
-      </c>
-      <c r="V102" s="3">
-        <v>-400</v>
       </c>
       <c r="W102" s="3">
         <v>-600</v>
       </c>
       <c r="X102" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Y102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OBLG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OBLG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
   <si>
     <t>OBLG</t>
   </si>
@@ -656,125 +656,129 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -782,239 +786,248 @@
         <v>600</v>
       </c>
       <c r="E8" s="3">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="F8" s="3">
         <v>900</v>
       </c>
       <c r="G8" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="H8" s="3">
         <v>1000</v>
       </c>
       <c r="I8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J8" s="3">
         <v>1400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5400</v>
-      </c>
-      <c r="V8" s="3">
-        <v>2400</v>
       </c>
       <c r="W8" s="3">
         <v>2400</v>
       </c>
       <c r="X8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Y8" s="3">
         <v>2600</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>2900</v>
       </c>
       <c r="Z8" s="3">
         <v>2900</v>
       </c>
       <c r="AA8" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AB8" s="3">
         <v>3300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>500</v>
+      </c>
+      <c r="E9" s="3">
         <v>600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>600</v>
-      </c>
-      <c r="G9" s="3">
-        <v>800</v>
       </c>
       <c r="H9" s="3">
         <v>800</v>
       </c>
       <c r="I9" s="3">
+        <v>800</v>
+      </c>
+      <c r="J9" s="3">
         <v>1100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1300</v>
-      </c>
-      <c r="N9" s="3">
-        <v>1200</v>
       </c>
       <c r="O9" s="3">
         <v>1200</v>
       </c>
       <c r="P9" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Q9" s="3">
         <v>1300</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>1600</v>
       </c>
       <c r="R9" s="3">
         <v>1600</v>
       </c>
       <c r="S9" s="3">
+        <v>1600</v>
+      </c>
+      <c r="T9" s="3">
         <v>4100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2500</v>
-      </c>
-      <c r="V9" s="3">
-        <v>1600</v>
       </c>
       <c r="W9" s="3">
         <v>1600</v>
       </c>
       <c r="X9" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="Y9" s="3">
         <v>1700</v>
       </c>
       <c r="Z9" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AA9" s="3">
         <v>1800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
         <v>200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>300</v>
-      </c>
-      <c r="G10" s="3">
-        <v>200</v>
       </c>
       <c r="H10" s="3">
         <v>200</v>
       </c>
       <c r="I10" s="3">
+        <v>200</v>
+      </c>
+      <c r="J10" s="3">
         <v>300</v>
-      </c>
-      <c r="J10" s="3">
-        <v>400</v>
       </c>
       <c r="K10" s="3">
         <v>400</v>
       </c>
       <c r="L10" s="3">
+        <v>400</v>
+      </c>
+      <c r="M10" s="3">
         <v>500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4000</v>
-      </c>
-      <c r="T10" s="3">
-        <v>2900</v>
       </c>
       <c r="U10" s="3">
         <v>2900</v>
       </c>
       <c r="V10" s="3">
-        <v>800</v>
+        <v>2900</v>
       </c>
       <c r="W10" s="3">
         <v>800</v>
       </c>
       <c r="X10" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y10" s="3">
         <v>900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1100</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>1400</v>
       </c>
       <c r="AB10" s="3">
         <v>1400</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,8 +1056,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1052,7 +1066,7 @@
         <v>100</v>
       </c>
       <c r="E12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F12" s="3">
         <v>0</v>
@@ -1064,46 +1078,46 @@
         <v>0</v>
       </c>
       <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
         <v>100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1400</v>
-      </c>
-      <c r="V12" s="3">
-        <v>200</v>
       </c>
       <c r="W12" s="3">
         <v>200</v>
@@ -1121,10 +1135,13 @@
         <v>200</v>
       </c>
       <c r="AB12" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC12" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1203,88 +1220,94 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>300</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>-400</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>5200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>6900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1100</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-2200</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-2600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>100</v>
-      </c>
-      <c r="S14" s="3">
-        <v>600</v>
       </c>
       <c r="T14" s="3">
         <v>600</v>
       </c>
       <c r="U14" s="3">
+        <v>600</v>
+      </c>
+      <c r="V14" s="3">
         <v>1800</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>500</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>1800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1292,7 +1315,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
         <v>100</v>
@@ -1307,7 +1330,7 @@
         <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>600</v>
@@ -1319,7 +1342,7 @@
         <v>600</v>
       </c>
       <c r="N15" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="O15" s="3">
         <v>700</v>
@@ -1331,22 +1354,22 @@
         <v>700</v>
       </c>
       <c r="R15" s="3">
+        <v>700</v>
+      </c>
+      <c r="S15" s="3">
         <v>800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>100</v>
-      </c>
-      <c r="W15" s="3">
-        <v>200</v>
       </c>
       <c r="X15" s="3">
         <v>200</v>
@@ -1363,8 +1386,11 @@
       <c r="AB15" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1416,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E17" s="3">
         <v>1800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>14400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-9100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-6300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1580,8 +1613,9 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1592,19 +1626,19 @@
         <v>100</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
         <v>100</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1619,11 +1653,11 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1637,11 +1671,11 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
@@ -1649,104 +1683,110 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-200</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-1100</v>
+        <v>-1000</v>
       </c>
       <c r="E21" s="3">
         <v>-1100</v>
       </c>
       <c r="F21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="G21" s="3">
         <v>-800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1000</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-1100</v>
       </c>
       <c r="I21" s="3">
         <v>-1100</v>
       </c>
       <c r="J21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="K21" s="3">
         <v>-6600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-8400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2200</v>
       </c>
-      <c r="N21" s="3">
-        <v>0</v>
-      </c>
       <c r="O21" s="3">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3">
         <v>-1500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-4700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-4700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
@@ -1763,12 +1803,12 @@
       <c r="I22" s="3">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -1788,19 +1828,19 @@
         <v>0</v>
       </c>
       <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>200</v>
-      </c>
-      <c r="T22" s="3">
-        <v>100</v>
       </c>
       <c r="U22" s="3">
         <v>100</v>
       </c>
       <c r="V22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -1808,100 +1848,106 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-      <c r="Y22" s="3" t="s">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
       <c r="AA22" s="3">
         <v>0</v>
       </c>
       <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1000</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-1200</v>
       </c>
       <c r="I23" s="3">
         <v>-1200</v>
       </c>
       <c r="J23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K23" s="3">
         <v>-7200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1933,11 +1979,11 @@
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
@@ -1945,10 +1991,10 @@
         <v>0</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>100</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>17</v>
@@ -1968,8 +2014,8 @@
       <c r="X24" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
+      <c r="Y24" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="Z24" s="3">
         <v>0</v>
@@ -1980,8 +2026,11 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2109,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1000</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-1200</v>
       </c>
       <c r="I26" s="3">
         <v>-1200</v>
       </c>
       <c r="J26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K26" s="3">
         <v>-7200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-6500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1900</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-1200</v>
       </c>
       <c r="I27" s="3">
         <v>-1200</v>
       </c>
       <c r="J27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K27" s="3">
         <v>-7200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2380,8 +2441,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,8 +2607,11 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2552,19 +2622,19 @@
         <v>-100</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
         <v>-100</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2579,11 +2649,11 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -2597,11 +2667,11 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
@@ -2609,99 +2679,105 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>200</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1900</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-1200</v>
       </c>
       <c r="I33" s="3">
         <v>-1200</v>
       </c>
       <c r="J33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K33" s="3">
         <v>-7200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2856,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1900</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-1200</v>
       </c>
       <c r="I35" s="3">
         <v>-1200</v>
       </c>
       <c r="J35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K35" s="3">
         <v>-7200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,88 +3091,92 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E41" s="3">
         <v>5400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>13000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3165,8 +3255,11 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3174,16 +3267,16 @@
         <v>0</v>
       </c>
       <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3">
         <v>400</v>
-      </c>
-      <c r="F43" s="3">
-        <v>200</v>
       </c>
       <c r="G43" s="3">
         <v>200</v>
       </c>
       <c r="H43" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="I43" s="3">
         <v>400</v>
@@ -3192,46 +3285,46 @@
         <v>400</v>
       </c>
       <c r="K43" s="3">
+        <v>400</v>
+      </c>
+      <c r="L43" s="3">
         <v>500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1500</v>
-      </c>
-      <c r="X43" s="3">
-        <v>1400</v>
       </c>
       <c r="Y43" s="3">
         <v>1400</v>
@@ -3240,13 +3333,16 @@
         <v>1400</v>
       </c>
       <c r="AA43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AB43" s="3">
         <v>1500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3254,58 +3350,58 @@
         <v>100</v>
       </c>
       <c r="E44" s="3">
+        <v>100</v>
+      </c>
+      <c r="F44" s="3">
         <v>200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1800</v>
-      </c>
-      <c r="V44" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="W44" s="3" t="s">
         <v>17</v>
@@ -3325,76 +3421,79 @@
       <c r="AB44" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>300</v>
+      </c>
+      <c r="E45" s="3">
         <v>400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1100</v>
-      </c>
-      <c r="N45" s="3">
-        <v>1500</v>
       </c>
       <c r="O45" s="3">
         <v>1500</v>
       </c>
       <c r="P45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q45" s="3">
         <v>1200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>600</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>500</v>
       </c>
       <c r="Z45" s="3">
         <v>500</v>
@@ -3403,90 +3502,96 @@
         <v>500</v>
       </c>
       <c r="AB45" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC45" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E46" s="3">
         <v>5900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>15400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>17600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>7800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>8800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>9900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3565,8 +3670,11 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3580,7 +3688,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3">
         <v>100</v>
@@ -3589,55 +3697,55 @@
         <v>100</v>
       </c>
       <c r="J48" s="3">
+        <v>100</v>
+      </c>
+      <c r="K48" s="3">
         <v>200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>700</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>1000</v>
       </c>
       <c r="AA48" s="3">
         <v>1000</v>
@@ -3645,88 +3753,94 @@
       <c r="AB48" s="3">
         <v>1000</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E49" s="3">
-        <v>0</v>
+      <c r="E49" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
         <v>300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>13200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>15500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>16300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>16900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>17500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>18100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>18700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>19300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>20500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2800</v>
-      </c>
-      <c r="X49" s="3">
-        <v>3300</v>
       </c>
       <c r="Y49" s="3">
         <v>3300</v>
       </c>
       <c r="Z49" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AA49" s="3">
         <v>5100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>6100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,8 +4002,11 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3909,13 +4029,13 @@
         <v>0</v>
       </c>
       <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M52" s="3">
         <v>100</v>
@@ -3930,10 +4050,10 @@
         <v>100</v>
       </c>
       <c r="Q52" s="3">
+        <v>100</v>
+      </c>
+      <c r="R52" s="3">
         <v>200</v>
-      </c>
-      <c r="R52" s="3">
-        <v>100</v>
       </c>
       <c r="S52" s="3">
         <v>100</v>
@@ -3945,16 +4065,16 @@
         <v>100</v>
       </c>
       <c r="V52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X52" s="3">
         <v>100</v>
       </c>
       <c r="Y52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z52" s="3">
         <v>0</v>
@@ -3965,8 +4085,11 @@
       <c r="AB52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,88 +4168,94 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E54" s="3">
         <v>5900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>24200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>28600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>31700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>34900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>26700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>29100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>27200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>29300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>32000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>34900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>8000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>10500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>11900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>13800</v>
       </c>
     </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,88 +4315,92 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>100</v>
+      </c>
+      <c r="E57" s="3">
         <v>400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>200</v>
-      </c>
-      <c r="F57" s="3">
-        <v>100</v>
       </c>
       <c r="G57" s="3">
         <v>100</v>
       </c>
       <c r="H57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I57" s="3">
         <v>200</v>
       </c>
       <c r="J57" s="3">
+        <v>200</v>
+      </c>
+      <c r="K57" s="3">
         <v>400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>300</v>
-      </c>
-      <c r="N57" s="3">
-        <v>500</v>
       </c>
       <c r="O57" s="3">
         <v>500</v>
       </c>
       <c r="P57" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q57" s="3">
         <v>1100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>300</v>
-      </c>
-      <c r="X57" s="3">
-        <v>200</v>
       </c>
       <c r="Y57" s="3">
         <v>200</v>
       </c>
       <c r="Z57" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA57" s="3">
         <v>400</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>300</v>
       </c>
       <c r="AB57" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4307,25 +4441,25 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>2400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2700</v>
-      </c>
-      <c r="V58" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>17</v>
@@ -4333,8 +4467,8 @@
       <c r="X58" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
@@ -4345,8 +4479,11 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4354,159 +4491,165 @@
         <v>1100</v>
       </c>
       <c r="E59" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="F59" s="3">
         <v>1200</v>
       </c>
       <c r="G59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H59" s="3">
         <v>1100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1700</v>
-      </c>
-      <c r="J59" s="3">
-        <v>2000</v>
       </c>
       <c r="K59" s="3">
         <v>2000</v>
       </c>
       <c r="L59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M59" s="3">
         <v>2300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>900</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>700</v>
       </c>
       <c r="AA59" s="3">
         <v>700</v>
       </c>
       <c r="AB59" s="3">
+        <v>700</v>
+      </c>
+      <c r="AC59" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E60" s="3">
         <v>1500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1900</v>
-      </c>
-      <c r="J60" s="3">
-        <v>2400</v>
       </c>
       <c r="K60" s="3">
         <v>2400</v>
       </c>
       <c r="L60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="M60" s="3">
         <v>2800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>10000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1400</v>
-      </c>
-      <c r="Y60" s="3">
-        <v>1100</v>
       </c>
       <c r="Z60" s="3">
         <v>1100</v>
       </c>
       <c r="AA60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AB60" s="3">
         <v>1000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4544,29 +4687,29 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>2400</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2800</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4585,8 +4728,11 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4600,7 +4746,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H62" s="3">
         <v>100</v>
@@ -4609,16 +4755,16 @@
         <v>100</v>
       </c>
       <c r="J62" s="3">
+        <v>100</v>
+      </c>
+      <c r="K62" s="3">
         <v>200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>500</v>
-      </c>
-      <c r="M62" s="3">
-        <v>600</v>
       </c>
       <c r="N62" s="3">
         <v>600</v>
@@ -4627,25 +4773,25 @@
         <v>600</v>
       </c>
       <c r="P62" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q62" s="3">
         <v>1000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2000</v>
-      </c>
-      <c r="V62" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>17</v>
@@ -4665,8 +4811,11 @@
       <c r="AB62" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,88 +5060,94 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1400</v>
-      </c>
-      <c r="F66" s="3">
-        <v>1300</v>
       </c>
       <c r="G66" s="3">
         <v>1300</v>
       </c>
       <c r="H66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I66" s="3">
         <v>2400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2000</v>
-      </c>
-      <c r="J66" s="3">
-        <v>2600</v>
       </c>
       <c r="K66" s="3">
         <v>2600</v>
       </c>
       <c r="L66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="M66" s="3">
         <v>3300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7100</v>
-      </c>
-      <c r="R66" s="3">
-        <v>13900</v>
       </c>
       <c r="S66" s="3">
         <v>13900</v>
       </c>
       <c r="T66" s="3">
+        <v>13900</v>
+      </c>
+      <c r="U66" s="3">
         <v>13200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1400</v>
-      </c>
-      <c r="Y66" s="3">
-        <v>1100</v>
       </c>
       <c r="Z66" s="3">
         <v>1100</v>
       </c>
       <c r="AA66" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AB66" s="3">
         <v>1000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5255,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,88 +5506,94 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-230400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-229400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-228200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-227000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-226100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-225100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-223800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-222600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-215500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-206400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-201900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-199200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-198500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-196300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-192900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-194000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-191900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-188600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-185400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-179800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-179100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-178300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-177700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-174900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-173500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-171800</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,88 +5838,94 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E76" s="3">
         <v>4400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>25500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>28100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>28300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>18900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>22100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>15400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>18800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>21800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>6200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>6800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>9500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>10900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6004,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1900</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-1200</v>
       </c>
       <c r="I81" s="3">
         <v>-1200</v>
       </c>
       <c r="J81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K81" s="3">
         <v>-7200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,8 +6208,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6019,7 +6218,7 @@
         <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
         <v>100</v>
@@ -6034,7 +6233,7 @@
         <v>100</v>
       </c>
       <c r="J83" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="K83" s="3">
         <v>600</v>
@@ -6046,7 +6245,7 @@
         <v>600</v>
       </c>
       <c r="N83" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="O83" s="3">
         <v>700</v>
@@ -6058,22 +6257,22 @@
         <v>700</v>
       </c>
       <c r="R83" s="3">
+        <v>700</v>
+      </c>
+      <c r="S83" s="3">
         <v>800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>100</v>
-      </c>
-      <c r="W83" s="3">
-        <v>200</v>
       </c>
       <c r="X83" s="3">
         <v>200</v>
@@ -6090,8 +6289,11 @@
       <c r="AB83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,88 +6704,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,8 +6820,9 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6653,12 +6874,12 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
@@ -6672,16 +6893,19 @@
         <v>0</v>
       </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-200</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,16 +7067,19 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
+      <c r="E94" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
@@ -6897,11 +7127,11 @@
         <v>0</v>
       </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>2200</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
         <v>0</v>
       </c>
@@ -6912,16 +7142,19 @@
         <v>0</v>
       </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-200</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7183,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7030,8 +7264,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,68 +7513,71 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>4500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1500</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>17</v>
+      <c r="K100" s="3">
+        <v>0</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>11500</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>4900</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>2400</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>3800</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
@@ -7342,16 +7588,19 @@
         <v>0</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-100</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7430,84 +7679,90 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>9100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>3300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OBLG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OBLG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
   <si>
     <t>OBLG</t>
   </si>
@@ -656,129 +656,133 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -789,79 +793,82 @@
         <v>600</v>
       </c>
       <c r="F8" s="3">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="G8" s="3">
         <v>900</v>
       </c>
       <c r="H8" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="I8" s="3">
         <v>1000</v>
       </c>
       <c r="J8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K8" s="3">
         <v>1400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5400</v>
-      </c>
-      <c r="W8" s="3">
-        <v>2400</v>
       </c>
       <c r="X8" s="3">
         <v>2400</v>
       </c>
       <c r="Y8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Z8" s="3">
         <v>2600</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>2900</v>
       </c>
       <c r="AA8" s="3">
         <v>2900</v>
       </c>
       <c r="AB8" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AC8" s="3">
         <v>3300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -869,82 +876,85 @@
         <v>500</v>
       </c>
       <c r="E9" s="3">
+        <v>500</v>
+      </c>
+      <c r="F9" s="3">
         <v>600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>600</v>
-      </c>
-      <c r="H9" s="3">
-        <v>800</v>
       </c>
       <c r="I9" s="3">
         <v>800</v>
       </c>
       <c r="J9" s="3">
+        <v>800</v>
+      </c>
+      <c r="K9" s="3">
         <v>1100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1300</v>
-      </c>
-      <c r="O9" s="3">
-        <v>1200</v>
       </c>
       <c r="P9" s="3">
         <v>1200</v>
       </c>
       <c r="Q9" s="3">
+        <v>1200</v>
+      </c>
+      <c r="R9" s="3">
         <v>1300</v>
-      </c>
-      <c r="R9" s="3">
-        <v>1600</v>
       </c>
       <c r="S9" s="3">
         <v>1600</v>
       </c>
       <c r="T9" s="3">
+        <v>1600</v>
+      </c>
+      <c r="U9" s="3">
         <v>4100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2500</v>
-      </c>
-      <c r="W9" s="3">
-        <v>1600</v>
       </c>
       <c r="X9" s="3">
         <v>1600</v>
       </c>
       <c r="Y9" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="Z9" s="3">
         <v>1700</v>
       </c>
       <c r="AA9" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AB9" s="3">
         <v>1800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -952,10 +962,10 @@
         <v>100</v>
       </c>
       <c r="E10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F10" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3">
         <v>300</v>
@@ -964,70 +974,73 @@
         <v>200</v>
       </c>
       <c r="I10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J10" s="3">
         <v>300</v>
       </c>
       <c r="K10" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="L10" s="3">
         <v>400</v>
       </c>
       <c r="M10" s="3">
+        <v>400</v>
+      </c>
+      <c r="N10" s="3">
         <v>500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4000</v>
-      </c>
-      <c r="U10" s="3">
-        <v>2900</v>
       </c>
       <c r="V10" s="3">
         <v>2900</v>
       </c>
       <c r="W10" s="3">
-        <v>800</v>
+        <v>2900</v>
       </c>
       <c r="X10" s="3">
         <v>800</v>
       </c>
       <c r="Y10" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z10" s="3">
         <v>900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1100</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>1400</v>
       </c>
       <c r="AC10" s="3">
         <v>1400</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1057,19 +1070,20 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E12" s="3">
         <v>100</v>
       </c>
       <c r="F12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12" s="3">
         <v>0</v>
@@ -1081,46 +1095,46 @@
         <v>0</v>
       </c>
       <c r="J12" s="3">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3">
         <v>100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1400</v>
-      </c>
-      <c r="W12" s="3">
-        <v>200</v>
       </c>
       <c r="X12" s="3">
         <v>200</v>
@@ -1138,10 +1152,13 @@
         <v>200</v>
       </c>
       <c r="AC12" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD12" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1223,99 +1240,105 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>-400</v>
+      <c r="H14" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>5200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>6900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1100</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-2200</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-2600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>100</v>
-      </c>
-      <c r="T14" s="3">
-        <v>600</v>
       </c>
       <c r="U14" s="3">
         <v>600</v>
       </c>
       <c r="V14" s="3">
+        <v>600</v>
+      </c>
+      <c r="W14" s="3">
         <v>1800</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>500</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>1800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
         <v>100</v>
@@ -1333,7 +1356,7 @@
         <v>100</v>
       </c>
       <c r="K15" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
         <v>600</v>
@@ -1345,7 +1368,7 @@
         <v>600</v>
       </c>
       <c r="O15" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="P15" s="3">
         <v>700</v>
@@ -1357,22 +1380,22 @@
         <v>700</v>
       </c>
       <c r="S15" s="3">
+        <v>700</v>
+      </c>
+      <c r="T15" s="3">
         <v>800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>100</v>
-      </c>
-      <c r="X15" s="3">
-        <v>200</v>
       </c>
       <c r="Y15" s="3">
         <v>200</v>
@@ -1389,8 +1412,11 @@
       <c r="AC15" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1443,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E17" s="3">
         <v>1600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J17" s="3">
         <v>2200</v>
       </c>
-      <c r="G17" s="3">
-        <v>1800</v>
-      </c>
-      <c r="H17" s="3">
-        <v>2000</v>
-      </c>
-      <c r="I17" s="3">
-        <v>2200</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>14400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K18" s="3">
         <v>-1300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="L18" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="O18" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="R18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="S18" s="3">
+        <v>1300</v>
+      </c>
+      <c r="T18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="U18" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="V18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="W18" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="X18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-900</v>
       </c>
-      <c r="H18" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-9100</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-700</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="Z18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q18" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="R18" s="3">
-        <v>1300</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-600</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="AB18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-900</v>
       </c>
-      <c r="Y18" s="3">
-        <v>-600</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>-900</v>
-      </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1614,35 +1647,36 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
-        <v>100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>100</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1656,11 +1690,11 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>300</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1674,11 +1708,11 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
@@ -1686,19 +1720,22 @@
         <v>0</v>
       </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-200</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -1706,111 +1743,114 @@
         <v>-1000</v>
       </c>
       <c r="E21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G21" s="3">
         <v>-1100</v>
       </c>
-      <c r="F21" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1000</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-1100</v>
       </c>
       <c r="J21" s="3">
         <v>-1100</v>
       </c>
       <c r="K21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="L21" s="3">
         <v>-6600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-8400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2200</v>
       </c>
-      <c r="O21" s="3">
-        <v>0</v>
-      </c>
       <c r="P21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-4700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-4700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-2600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
+      <c r="E22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="H22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1831,19 +1871,19 @@
         <v>0</v>
       </c>
       <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
         <v>100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>200</v>
-      </c>
-      <c r="U22" s="3">
-        <v>100</v>
       </c>
       <c r="V22" s="3">
         <v>100</v>
       </c>
       <c r="W22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -1851,20 +1891,23 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
       </c>
       <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1872,102 +1915,105 @@
         <v>-1000</v>
       </c>
       <c r="E23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1000</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-1200</v>
       </c>
       <c r="J23" s="3">
         <v>-1200</v>
       </c>
       <c r="K23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="L23" s="3">
         <v>-7200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-6500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-5600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
+      <c r="F24" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
+      <c r="H24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="J24" s="3">
         <v>0</v>
@@ -1982,11 +2028,11 @@
         <v>0</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
@@ -1994,11 +2040,11 @@
         <v>0</v>
       </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>17</v>
       </c>
@@ -2017,8 +2063,8 @@
       <c r="Y24" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
+      <c r="Z24" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="AA24" s="3">
         <v>0</v>
@@ -2029,8 +2075,11 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,8 +2161,11 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2121,165 +2173,171 @@
         <v>-1000</v>
       </c>
       <c r="E26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1000</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-1200</v>
       </c>
       <c r="J26" s="3">
         <v>-1200</v>
       </c>
       <c r="K26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="L26" s="3">
         <v>-7200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-6500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-5600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1900</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-1200</v>
       </c>
       <c r="J27" s="3">
         <v>-1200</v>
       </c>
       <c r="K27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="L27" s="3">
         <v>-7200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-6500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-5700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,35 +2677,38 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I32" s="3">
+        <v>400</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -2652,11 +2722,11 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-300</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -2670,11 +2740,11 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
@@ -2682,19 +2752,22 @@
         <v>0</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>200</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2702,82 +2775,85 @@
         <v>-1000</v>
       </c>
       <c r="E33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="G33" s="3">
         <v>-1200</v>
       </c>
-      <c r="F33" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I33" s="3">
         <v>-1000</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-1200</v>
       </c>
       <c r="J33" s="3">
         <v>-1200</v>
       </c>
       <c r="K33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="L33" s="3">
         <v>-7200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-6500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-5700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,8 +2935,11 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2868,170 +2947,176 @@
         <v>-1000</v>
       </c>
       <c r="E35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="G35" s="3">
         <v>-1200</v>
       </c>
-      <c r="F35" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I35" s="3">
         <v>-1000</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-1200</v>
       </c>
       <c r="J35" s="3">
         <v>-1200</v>
       </c>
       <c r="K35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="L35" s="3">
         <v>-7200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-6500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-5700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,91 +3178,95 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E41" s="3">
         <v>5900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>13000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3258,8 +3348,11 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3270,16 +3363,16 @@
         <v>0</v>
       </c>
       <c r="F43" s="3">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3">
         <v>400</v>
-      </c>
-      <c r="G43" s="3">
-        <v>200</v>
       </c>
       <c r="H43" s="3">
         <v>200</v>
       </c>
       <c r="I43" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="J43" s="3">
         <v>400</v>
@@ -3288,46 +3381,46 @@
         <v>400</v>
       </c>
       <c r="L43" s="3">
+        <v>400</v>
+      </c>
+      <c r="M43" s="3">
         <v>500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1500</v>
-      </c>
-      <c r="Y43" s="3">
-        <v>1400</v>
       </c>
       <c r="Z43" s="3">
         <v>1400</v>
@@ -3336,13 +3429,16 @@
         <v>1400</v>
       </c>
       <c r="AB43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AC43" s="3">
         <v>1500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3353,59 +3449,59 @@
         <v>100</v>
       </c>
       <c r="F44" s="3">
+        <v>100</v>
+      </c>
+      <c r="G44" s="3">
         <v>200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1800</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>17</v>
       </c>
@@ -3424,79 +3520,82 @@
       <c r="AC44" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>300</v>
-      </c>
-      <c r="E45" s="3">
-        <v>400</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G45" s="3">
         <v>200</v>
       </c>
-      <c r="G45" s="3">
-        <v>300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>800</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K45" s="3">
+        <v>600</v>
+      </c>
+      <c r="L45" s="3">
         <v>900</v>
       </c>
-      <c r="J45" s="3">
-        <v>600</v>
-      </c>
-      <c r="K45" s="3">
-        <v>900</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1100</v>
-      </c>
-      <c r="O45" s="3">
-        <v>1500</v>
       </c>
       <c r="P45" s="3">
         <v>1500</v>
       </c>
       <c r="Q45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="R45" s="3">
         <v>1200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>600</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>500</v>
       </c>
       <c r="AA45" s="3">
         <v>500</v>
@@ -3505,116 +3604,122 @@
         <v>500</v>
       </c>
       <c r="AC45" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD45" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E46" s="3">
         <v>6300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>17600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>10000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>7800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>8800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>9900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3673,25 +3778,28 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>0</v>
-      </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
+      <c r="D48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G48" s="3">
         <v>0</v>
       </c>
       <c r="H48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3">
         <v>100</v>
@@ -3700,55 +3808,55 @@
         <v>100</v>
       </c>
       <c r="K48" s="3">
+        <v>100</v>
+      </c>
+      <c r="L48" s="3">
         <v>200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>700</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>1000</v>
       </c>
       <c r="AB48" s="3">
         <v>1000</v>
@@ -3756,91 +3864,97 @@
       <c r="AC48" s="3">
         <v>1000</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>17</v>
+      <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
       </c>
       <c r="F49" s="3">
         <v>0</v>
       </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>15500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>16300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>16900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>17500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>18100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>18700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>19300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>20500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2800</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>3300</v>
       </c>
       <c r="Z49" s="3">
         <v>3300</v>
       </c>
       <c r="AA49" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AB49" s="3">
         <v>5100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>6100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,8 +4122,11 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4032,13 +4152,13 @@
         <v>0</v>
       </c>
       <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
         <v>100</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N52" s="3">
         <v>100</v>
@@ -4053,10 +4173,10 @@
         <v>100</v>
       </c>
       <c r="R52" s="3">
+        <v>100</v>
+      </c>
+      <c r="S52" s="3">
         <v>200</v>
-      </c>
-      <c r="S52" s="3">
-        <v>100</v>
       </c>
       <c r="T52" s="3">
         <v>100</v>
@@ -4068,16 +4188,16 @@
         <v>100</v>
       </c>
       <c r="W52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y52" s="3">
         <v>100</v>
       </c>
       <c r="Z52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA52" s="3">
         <v>0</v>
@@ -4088,8 +4208,11 @@
       <c r="AC52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,91 +4294,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E54" s="3">
         <v>6300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>24200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>28600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>31700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>34900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>26700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>29100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>27200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>29300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>32000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>34900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>8000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>10500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>11900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>13800</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,8 +4446,9 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4325,82 +4456,85 @@
         <v>100</v>
       </c>
       <c r="E57" s="3">
+        <v>100</v>
+      </c>
+      <c r="F57" s="3">
         <v>400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>200</v>
-      </c>
-      <c r="G57" s="3">
-        <v>100</v>
       </c>
       <c r="H57" s="3">
         <v>100</v>
       </c>
       <c r="I57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J57" s="3">
         <v>200</v>
       </c>
       <c r="K57" s="3">
+        <v>200</v>
+      </c>
+      <c r="L57" s="3">
         <v>400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>300</v>
-      </c>
-      <c r="O57" s="3">
-        <v>500</v>
       </c>
       <c r="P57" s="3">
         <v>500</v>
       </c>
       <c r="Q57" s="3">
+        <v>500</v>
+      </c>
+      <c r="R57" s="3">
         <v>1100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>300</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>200</v>
       </c>
       <c r="Z57" s="3">
         <v>200</v>
       </c>
       <c r="AA57" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB57" s="3">
         <v>400</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>300</v>
       </c>
       <c r="AC57" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4420,10 +4554,10 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4444,34 +4578,34 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>2400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2700</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>17</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
+      <c r="Z58" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="AA58" s="3">
         <v>0</v>
@@ -4482,174 +4616,183 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1100</v>
+        <v>200</v>
       </c>
       <c r="E59" s="3">
-        <v>1100</v>
+        <v>200</v>
       </c>
       <c r="F59" s="3">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="G59" s="3">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="H59" s="3">
-        <v>1100</v>
+        <v>600</v>
       </c>
       <c r="I59" s="3">
-        <v>2100</v>
+        <v>600</v>
       </c>
       <c r="J59" s="3">
+        <v>700</v>
+      </c>
+      <c r="K59" s="3">
         <v>1700</v>
-      </c>
-      <c r="K59" s="3">
-        <v>2000</v>
       </c>
       <c r="L59" s="3">
         <v>2000</v>
       </c>
       <c r="M59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N59" s="3">
         <v>2300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>900</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>700</v>
       </c>
       <c r="AB59" s="3">
         <v>700</v>
       </c>
       <c r="AC59" s="3">
+        <v>700</v>
+      </c>
+      <c r="AD59" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E60" s="3">
         <v>1200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1900</v>
-      </c>
-      <c r="K60" s="3">
-        <v>2400</v>
       </c>
       <c r="L60" s="3">
         <v>2400</v>
       </c>
       <c r="M60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="N60" s="3">
         <v>2800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>10000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1400</v>
-      </c>
-      <c r="Z60" s="3">
-        <v>1100</v>
       </c>
       <c r="AA60" s="3">
         <v>1100</v>
       </c>
       <c r="AB60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AC60" s="3">
         <v>1000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4690,29 +4833,29 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>2400</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2800</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4731,43 +4874,46 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K62" s="3">
         <v>100</v>
       </c>
-      <c r="I62" s="3">
-        <v>100</v>
-      </c>
-      <c r="J62" s="3">
-        <v>100</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>500</v>
-      </c>
-      <c r="N62" s="3">
-        <v>600</v>
       </c>
       <c r="O62" s="3">
         <v>600</v>
@@ -4776,26 +4922,26 @@
         <v>600</v>
       </c>
       <c r="Q62" s="3">
+        <v>600</v>
+      </c>
+      <c r="R62" s="3">
         <v>1000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2000</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>17</v>
       </c>
@@ -4814,8 +4960,11 @@
       <c r="AC62" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,8 +5218,11 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5072,82 +5230,85 @@
         <v>1300</v>
       </c>
       <c r="E66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F66" s="3">
         <v>1500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1400</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1300</v>
       </c>
       <c r="H66" s="3">
         <v>1300</v>
       </c>
       <c r="I66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J66" s="3">
         <v>2400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2000</v>
-      </c>
-      <c r="K66" s="3">
-        <v>2600</v>
       </c>
       <c r="L66" s="3">
         <v>2600</v>
       </c>
       <c r="M66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="N66" s="3">
         <v>3300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7100</v>
-      </c>
-      <c r="S66" s="3">
-        <v>13900</v>
       </c>
       <c r="T66" s="3">
         <v>13900</v>
       </c>
       <c r="U66" s="3">
+        <v>13900</v>
+      </c>
+      <c r="V66" s="3">
         <v>13200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>13100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1400</v>
-      </c>
-      <c r="Z66" s="3">
-        <v>1100</v>
       </c>
       <c r="AA66" s="3">
         <v>1100</v>
       </c>
       <c r="AB66" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AC66" s="3">
         <v>1000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,91 +5680,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-231400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-230400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-229400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-228200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-227000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-226100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-225100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-223800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-222600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-215500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-206400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-201900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-199200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-198500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-196300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-192900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-194000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-191900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-188600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-185400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-179800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-179100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-178300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-177700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-174900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-173500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-171800</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,91 +6024,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E76" s="3">
         <v>5100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>25500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>28100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>28300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>18900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>22100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>15400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>18800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>21800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>6200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>9500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>10900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,96 +6196,102 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6104,82 +6299,85 @@
         <v>-1000</v>
       </c>
       <c r="E81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="G81" s="3">
         <v>-1200</v>
       </c>
-      <c r="F81" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I81" s="3">
         <v>-1000</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-1200</v>
       </c>
       <c r="J81" s="3">
         <v>-1200</v>
       </c>
       <c r="K81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="L81" s="3">
         <v>-7200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-6500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-5700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,34 +6407,35 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3">
         <v>100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>100</v>
-      </c>
-      <c r="I83" s="3">
-        <v>100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>100</v>
-      </c>
-      <c r="K83" s="3">
-        <v>600</v>
       </c>
       <c r="L83" s="3">
         <v>600</v>
@@ -6248,7 +6447,7 @@
         <v>600</v>
       </c>
       <c r="O83" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="P83" s="3">
         <v>700</v>
@@ -6260,22 +6459,22 @@
         <v>700</v>
       </c>
       <c r="S83" s="3">
+        <v>700</v>
+      </c>
+      <c r="T83" s="3">
         <v>800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>100</v>
-      </c>
-      <c r="X83" s="3">
-        <v>200</v>
       </c>
       <c r="Y83" s="3">
         <v>200</v>
@@ -6292,8 +6491,11 @@
       <c r="AC83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,91 +6921,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,31 +7041,32 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -6877,11 +7098,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -6896,16 +7117,19 @@
         <v>0</v>
       </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-200</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,8 +7297,11 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7081,20 +7311,20 @@
       <c r="E94" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="F94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -7130,11 +7360,11 @@
         <v>0</v>
       </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>2200</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
@@ -7145,16 +7375,19 @@
         <v>0</v>
       </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-200</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,31 +7417,32 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,71 +7759,74 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>700</v>
+      </c>
+      <c r="E100" s="3">
         <v>1500</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>4500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1500</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>17</v>
+      <c r="L100" s="3">
+        <v>0</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
+      <c r="N100" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>11500</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>4900</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>2400</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>3800</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
@@ -7591,39 +7837,42 @@
         <v>0</v>
       </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-100</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7682,87 +7931,93 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E102" s="3">
         <v>500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>9100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OBLG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OBLG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
   <si>
     <t>OBLG</t>
   </si>
@@ -656,133 +656,136 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -796,165 +799,171 @@
         <v>600</v>
       </c>
       <c r="G8" s="3">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="H8" s="3">
         <v>900</v>
       </c>
       <c r="I8" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="J8" s="3">
         <v>1000</v>
       </c>
       <c r="K8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L8" s="3">
         <v>1400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5400</v>
-      </c>
-      <c r="X8" s="3">
-        <v>2400</v>
       </c>
       <c r="Y8" s="3">
         <v>2400</v>
       </c>
       <c r="Z8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AA8" s="3">
         <v>2600</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>2900</v>
       </c>
       <c r="AB8" s="3">
         <v>2900</v>
       </c>
       <c r="AC8" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AD8" s="3">
         <v>3300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E9" s="3">
         <v>500</v>
       </c>
       <c r="F9" s="3">
+        <v>500</v>
+      </c>
+      <c r="G9" s="3">
         <v>600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>600</v>
-      </c>
-      <c r="I9" s="3">
-        <v>800</v>
       </c>
       <c r="J9" s="3">
         <v>800</v>
       </c>
       <c r="K9" s="3">
+        <v>800</v>
+      </c>
+      <c r="L9" s="3">
         <v>1100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1300</v>
-      </c>
-      <c r="P9" s="3">
-        <v>1200</v>
       </c>
       <c r="Q9" s="3">
         <v>1200</v>
       </c>
       <c r="R9" s="3">
+        <v>1200</v>
+      </c>
+      <c r="S9" s="3">
         <v>1300</v>
-      </c>
-      <c r="S9" s="3">
-        <v>1600</v>
       </c>
       <c r="T9" s="3">
         <v>1600</v>
       </c>
       <c r="U9" s="3">
+        <v>1600</v>
+      </c>
+      <c r="V9" s="3">
         <v>4100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2500</v>
-      </c>
-      <c r="X9" s="3">
-        <v>1600</v>
       </c>
       <c r="Y9" s="3">
         <v>1600</v>
       </c>
       <c r="Z9" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="AA9" s="3">
         <v>1700</v>
       </c>
       <c r="AB9" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AC9" s="3">
         <v>1800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -965,82 +974,85 @@
         <v>100</v>
       </c>
       <c r="F10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
         <v>300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>100</v>
-      </c>
-      <c r="J10" s="3">
-        <v>300</v>
       </c>
       <c r="K10" s="3">
         <v>300</v>
       </c>
       <c r="L10" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="M10" s="3">
         <v>400</v>
       </c>
       <c r="N10" s="3">
+        <v>400</v>
+      </c>
+      <c r="O10" s="3">
         <v>500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>4000</v>
-      </c>
-      <c r="V10" s="3">
-        <v>2900</v>
       </c>
       <c r="W10" s="3">
         <v>2900</v>
       </c>
       <c r="X10" s="3">
-        <v>800</v>
+        <v>2900</v>
       </c>
       <c r="Y10" s="3">
         <v>800</v>
       </c>
       <c r="Z10" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA10" s="3">
         <v>900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1100</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>1400</v>
       </c>
       <c r="AD10" s="3">
         <v>1400</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1071,8 +1083,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1080,13 +1093,13 @@
         <v>0</v>
       </c>
       <c r="E12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F12" s="3">
         <v>100</v>
       </c>
       <c r="G12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H12" s="3">
         <v>0</v>
@@ -1098,46 +1111,46 @@
         <v>0</v>
       </c>
       <c r="K12" s="3">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3">
         <v>100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1400</v>
-      </c>
-      <c r="X12" s="3">
-        <v>200</v>
       </c>
       <c r="Y12" s="3">
         <v>200</v>
@@ -1155,10 +1168,13 @@
         <v>200</v>
       </c>
       <c r="AD12" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE12" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1243,8 +1259,11 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1257,80 +1276,83 @@
       <c r="F14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="3">
         <v>300</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>5200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>6900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1100</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-2600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>100</v>
-      </c>
-      <c r="U14" s="3">
-        <v>600</v>
       </c>
       <c r="V14" s="3">
         <v>600</v>
       </c>
       <c r="W14" s="3">
+        <v>600</v>
+      </c>
+      <c r="X14" s="3">
         <v>1800</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>500</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>1800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1359,7 +1381,7 @@
         <v>100</v>
       </c>
       <c r="L15" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="M15" s="3">
         <v>600</v>
@@ -1371,7 +1393,7 @@
         <v>600</v>
       </c>
       <c r="P15" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="Q15" s="3">
         <v>700</v>
@@ -1383,22 +1405,22 @@
         <v>700</v>
       </c>
       <c r="T15" s="3">
+        <v>700</v>
+      </c>
+      <c r="U15" s="3">
         <v>800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>100</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>200</v>
       </c>
       <c r="Z15" s="3">
         <v>200</v>
@@ -1415,8 +1437,11 @@
       <c r="AD15" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E17" s="3">
         <v>1700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>14400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-9100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-6300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1648,8 +1680,9 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1659,27 +1692,27 @@
       <c r="E20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
+      <c r="F20" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="3">
         <v>-400</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1693,11 +1726,11 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>300</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -1711,11 +1744,11 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
@@ -1723,105 +1756,111 @@
         <v>0</v>
       </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-200</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1000</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-1100</v>
       </c>
       <c r="K21" s="3">
         <v>-1100</v>
       </c>
       <c r="L21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="M21" s="3">
         <v>-6600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-8400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-3900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2200</v>
       </c>
-      <c r="P21" s="3">
-        <v>0</v>
-      </c>
       <c r="Q21" s="3">
+        <v>0</v>
+      </c>
+      <c r="R21" s="3">
         <v>-1500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-4700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-4700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1834,26 +1873,26 @@
       <c r="F22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>17</v>
+      <c r="G22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="J22" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1874,19 +1913,19 @@
         <v>0</v>
       </c>
       <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>200</v>
-      </c>
-      <c r="V22" s="3">
-        <v>100</v>
       </c>
       <c r="W22" s="3">
         <v>100</v>
       </c>
       <c r="X22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
@@ -1894,129 +1933,135 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
       </c>
       <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-1000</v>
+        <v>-900</v>
       </c>
       <c r="E23" s="3">
         <v>-1000</v>
       </c>
       <c r="F23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G23" s="3">
         <v>-1100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1000</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-1200</v>
       </c>
       <c r="K23" s="3">
         <v>-1200</v>
       </c>
       <c r="L23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="M23" s="3">
         <v>-7200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-6500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>17</v>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="J24" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -2031,11 +2076,11 @@
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
@@ -2043,11 +2088,11 @@
         <v>0</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>17</v>
       </c>
@@ -2066,8 +2111,8 @@
       <c r="Z24" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
+      <c r="AA24" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="AB24" s="3">
         <v>0</v>
@@ -2078,8 +2123,11 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-1000</v>
+        <v>-900</v>
       </c>
       <c r="E26" s="3">
         <v>-1000</v>
       </c>
       <c r="F26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G26" s="3">
         <v>-1100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1000</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-1200</v>
       </c>
       <c r="K26" s="3">
         <v>-1200</v>
       </c>
       <c r="L26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="M26" s="3">
         <v>-7200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-6500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-5600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-10000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1900</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-1200</v>
       </c>
       <c r="K27" s="3">
         <v>-1200</v>
       </c>
       <c r="L27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="M27" s="3">
         <v>-7200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-6500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-5700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2508,8 +2568,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,8 +2746,11 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2691,27 +2760,27 @@
       <c r="E32" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
+      <c r="F32" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" s="3">
         <v>400</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -2725,11 +2794,11 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -2743,11 +2812,11 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
@@ -2755,105 +2824,111 @@
         <v>0</v>
       </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>200</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-1000</v>
+        <v>-900</v>
       </c>
       <c r="E33" s="3">
         <v>-1000</v>
       </c>
       <c r="F33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G33" s="3">
         <v>-1100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1000</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-1200</v>
       </c>
       <c r="K33" s="3">
         <v>-1200</v>
       </c>
       <c r="L33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="M33" s="3">
         <v>-7200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-6500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-5700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-1000</v>
+        <v>-900</v>
       </c>
       <c r="E35" s="3">
         <v>-1000</v>
       </c>
       <c r="F35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G35" s="3">
         <v>-1100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1000</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-1200</v>
       </c>
       <c r="K35" s="3">
         <v>-1200</v>
       </c>
       <c r="L35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="M35" s="3">
         <v>-7200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-6500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-5700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,94 +3264,98 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>13000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3351,13 +3440,16 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E43" s="3">
         <v>0</v>
@@ -3366,16 +3458,16 @@
         <v>0</v>
       </c>
       <c r="G43" s="3">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3">
         <v>400</v>
-      </c>
-      <c r="H43" s="3">
-        <v>200</v>
       </c>
       <c r="I43" s="3">
         <v>200</v>
       </c>
       <c r="J43" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="K43" s="3">
         <v>400</v>
@@ -3384,46 +3476,46 @@
         <v>400</v>
       </c>
       <c r="M43" s="3">
+        <v>400</v>
+      </c>
+      <c r="N43" s="3">
         <v>500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1500</v>
-      </c>
-      <c r="Z43" s="3">
-        <v>1400</v>
       </c>
       <c r="AA43" s="3">
         <v>1400</v>
@@ -3432,18 +3524,21 @@
         <v>1400</v>
       </c>
       <c r="AC43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AD43" s="3">
         <v>1500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>100</v>
+      <c r="D44" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E44" s="3">
         <v>100</v>
@@ -3452,59 +3547,59 @@
         <v>100</v>
       </c>
       <c r="G44" s="3">
+        <v>100</v>
+      </c>
+      <c r="H44" s="3">
         <v>200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1800</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="Y44" s="3" t="s">
         <v>17</v>
       </c>
@@ -3523,8 +3618,11 @@
       <c r="AD44" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3537,68 +3635,68 @@
       <c r="F45" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H45" s="3">
         <v>200</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L45" s="3">
         <v>600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1100</v>
-      </c>
-      <c r="P45" s="3">
-        <v>1500</v>
       </c>
       <c r="Q45" s="3">
         <v>1500</v>
       </c>
       <c r="R45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="S45" s="3">
         <v>1200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>600</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>500</v>
       </c>
       <c r="AB45" s="3">
         <v>500</v>
@@ -3607,96 +3705,102 @@
         <v>500</v>
       </c>
       <c r="AD45" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE45" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E46" s="3">
         <v>6000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>17600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>10000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>8800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>9900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3721,8 +3825,8 @@
       <c r="J47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3781,8 +3885,11 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3795,14 +3902,14 @@
       <c r="F48" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G48" s="3">
-        <v>0</v>
+      <c r="G48" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="H48" s="3">
         <v>0</v>
       </c>
       <c r="I48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3">
         <v>100</v>
@@ -3811,55 +3918,55 @@
         <v>100</v>
       </c>
       <c r="L48" s="3">
+        <v>100</v>
+      </c>
+      <c r="M48" s="3">
         <v>200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>700</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>1000</v>
       </c>
       <c r="AC48" s="3">
         <v>1000</v>
@@ -3867,8 +3974,11 @@
       <c r="AD48" s="3">
         <v>1000</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3885,76 +3995,79 @@
         <v>0</v>
       </c>
       <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
         <v>300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>13200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>14900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>15500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>16300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>16900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>17500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>18100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>18700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>19300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>20500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2800</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>3300</v>
       </c>
       <c r="AA49" s="3">
         <v>3300</v>
       </c>
       <c r="AB49" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AC49" s="3">
         <v>5100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>6100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,8 +4241,11 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4155,13 +4274,13 @@
         <v>0</v>
       </c>
       <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
         <v>100</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
       <c r="N52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O52" s="3">
         <v>100</v>
@@ -4176,10 +4295,10 @@
         <v>100</v>
       </c>
       <c r="S52" s="3">
+        <v>100</v>
+      </c>
+      <c r="T52" s="3">
         <v>200</v>
-      </c>
-      <c r="T52" s="3">
-        <v>100</v>
       </c>
       <c r="U52" s="3">
         <v>100</v>
@@ -4191,16 +4310,16 @@
         <v>100</v>
       </c>
       <c r="X52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z52" s="3">
         <v>100</v>
       </c>
       <c r="AA52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB52" s="3">
         <v>0</v>
@@ -4211,8 +4330,11 @@
       <c r="AD52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,94 +4419,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E54" s="3">
         <v>6000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>24200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>28600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>31700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>34900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>26700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>29100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>27200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>29300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>32000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>34900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>8000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>10500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>11900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>13800</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,8 +4576,9 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4459,82 +4589,85 @@
         <v>100</v>
       </c>
       <c r="F57" s="3">
+        <v>100</v>
+      </c>
+      <c r="G57" s="3">
         <v>400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>200</v>
-      </c>
-      <c r="H57" s="3">
-        <v>100</v>
       </c>
       <c r="I57" s="3">
         <v>100</v>
       </c>
       <c r="J57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K57" s="3">
         <v>200</v>
       </c>
       <c r="L57" s="3">
+        <v>200</v>
+      </c>
+      <c r="M57" s="3">
         <v>400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>300</v>
-      </c>
-      <c r="P57" s="3">
-        <v>500</v>
       </c>
       <c r="Q57" s="3">
         <v>500</v>
       </c>
       <c r="R57" s="3">
+        <v>500</v>
+      </c>
+      <c r="S57" s="3">
         <v>1100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>300</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>200</v>
       </c>
       <c r="AA57" s="3">
         <v>200</v>
       </c>
       <c r="AB57" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC57" s="3">
         <v>400</v>
-      </c>
-      <c r="AC57" s="3">
-        <v>300</v>
       </c>
       <c r="AD57" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4554,13 +4687,13 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3">
         <v>100</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -4581,34 +4714,34 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>2400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2700</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>17</v>
       </c>
       <c r="Z58" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
+      <c r="AA58" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="AB58" s="3">
         <v>0</v>
@@ -4619,94 +4752,100 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E59" s="3">
         <v>200</v>
       </c>
       <c r="F59" s="3">
+        <v>200</v>
+      </c>
+      <c r="G59" s="3">
         <v>300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>400</v>
-      </c>
-      <c r="H59" s="3">
-        <v>600</v>
       </c>
       <c r="I59" s="3">
         <v>600</v>
       </c>
       <c r="J59" s="3">
+        <v>600</v>
+      </c>
+      <c r="K59" s="3">
         <v>700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1700</v>
-      </c>
-      <c r="L59" s="3">
-        <v>2000</v>
       </c>
       <c r="M59" s="3">
         <v>2000</v>
       </c>
       <c r="N59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="O59" s="3">
         <v>2300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>900</v>
-      </c>
-      <c r="AB59" s="3">
-        <v>700</v>
       </c>
       <c r="AC59" s="3">
         <v>700</v>
       </c>
       <c r="AD59" s="3">
+        <v>700</v>
+      </c>
+      <c r="AE59" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4714,85 +4853,88 @@
         <v>1300</v>
       </c>
       <c r="E60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F60" s="3">
         <v>1200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1900</v>
-      </c>
-      <c r="L60" s="3">
-        <v>2400</v>
       </c>
       <c r="M60" s="3">
         <v>2400</v>
       </c>
       <c r="N60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="O60" s="3">
         <v>2800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>8300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1400</v>
-      </c>
-      <c r="AA60" s="3">
-        <v>1100</v>
       </c>
       <c r="AB60" s="3">
         <v>1100</v>
       </c>
       <c r="AC60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AD60" s="3">
         <v>1000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4836,29 +4978,29 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>2400</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2800</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4877,8 +5019,11 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4903,20 +5048,20 @@
       <c r="J62" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L62" s="3">
         <v>100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>500</v>
-      </c>
-      <c r="O62" s="3">
-        <v>600</v>
       </c>
       <c r="P62" s="3">
         <v>600</v>
@@ -4925,26 +5070,26 @@
         <v>600</v>
       </c>
       <c r="R62" s="3">
+        <v>600</v>
+      </c>
+      <c r="S62" s="3">
         <v>1000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2000</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>17</v>
       </c>
@@ -4963,8 +5108,11 @@
       <c r="AD62" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,8 +5375,11 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5233,82 +5390,85 @@
         <v>1300</v>
       </c>
       <c r="F66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G66" s="3">
         <v>1500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1400</v>
-      </c>
-      <c r="H66" s="3">
-        <v>1300</v>
       </c>
       <c r="I66" s="3">
         <v>1300</v>
       </c>
       <c r="J66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K66" s="3">
         <v>2400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2000</v>
-      </c>
-      <c r="L66" s="3">
-        <v>2600</v>
       </c>
       <c r="M66" s="3">
         <v>2600</v>
       </c>
       <c r="N66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="O66" s="3">
         <v>3300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7100</v>
-      </c>
-      <c r="T66" s="3">
-        <v>13900</v>
       </c>
       <c r="U66" s="3">
         <v>13900</v>
       </c>
       <c r="V66" s="3">
+        <v>13900</v>
+      </c>
+      <c r="W66" s="3">
         <v>13200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>13100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1400</v>
-      </c>
-      <c r="AA66" s="3">
-        <v>1100</v>
       </c>
       <c r="AB66" s="3">
         <v>1100</v>
       </c>
       <c r="AC66" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AD66" s="3">
         <v>1000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5597,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,94 +5853,100 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-232300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-231400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-230400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-229400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-228200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-227000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-226100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-225100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-223800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-222600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-215500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-206400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-201900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-199200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-198500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-196300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-192900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-194000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-191900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-188600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-185400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-179800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-179100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-178300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-177700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-174900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-173500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-171800</v>
       </c>
     </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,94 +6209,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E76" s="3">
         <v>4700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>25500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>28100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>28300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>18900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>22100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>15400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>18800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>21800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>9500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>10900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-1000</v>
+        <v>-900</v>
       </c>
       <c r="E81" s="3">
         <v>-1000</v>
       </c>
       <c r="F81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G81" s="3">
         <v>-1100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1000</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-1200</v>
       </c>
       <c r="K81" s="3">
         <v>-1200</v>
       </c>
       <c r="L81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="M81" s="3">
         <v>-7200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-6500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-5700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,8 +6605,9 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6422,8 +6620,8 @@
       <c r="F83" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G83" s="3">
-        <v>0</v>
+      <c r="G83" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="H83" s="3">
         <v>0</v>
@@ -6435,10 +6633,10 @@
         <v>0</v>
       </c>
       <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
         <v>100</v>
-      </c>
-      <c r="L83" s="3">
-        <v>600</v>
       </c>
       <c r="M83" s="3">
         <v>600</v>
@@ -6450,7 +6648,7 @@
         <v>600</v>
       </c>
       <c r="P83" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="Q83" s="3">
         <v>700</v>
@@ -6462,22 +6660,22 @@
         <v>700</v>
       </c>
       <c r="T83" s="3">
+        <v>700</v>
+      </c>
+      <c r="U83" s="3">
         <v>800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>100</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>200</v>
       </c>
       <c r="Z83" s="3">
         <v>200</v>
@@ -6494,8 +6692,11 @@
       <c r="AD83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,8 +7137,11 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6933,85 +7149,88 @@
         <v>-900</v>
       </c>
       <c r="E89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-2600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,8 +7261,9 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7068,8 +7288,8 @@
       <c r="J91" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -7101,11 +7321,11 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
@@ -7120,16 +7340,19 @@
         <v>0</v>
       </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-200</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,8 +7526,11 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7326,8 +7555,8 @@
       <c r="J94" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -7363,11 +7592,11 @@
         <v>0</v>
       </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>2200</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3">
         <v>0</v>
       </c>
@@ -7378,16 +7607,19 @@
         <v>0</v>
       </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-200</v>
       </c>
-      <c r="AD94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7444,8 +7677,8 @@
       <c r="J96" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7504,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,74 +8004,77 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>200</v>
+      </c>
+      <c r="E100" s="3">
         <v>700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1500</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>4500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1500</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>17</v>
+      <c r="M100" s="3">
+        <v>0</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
+      <c r="O100" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>11500</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>4900</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>2400</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>3800</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
@@ -7840,16 +8085,19 @@
         <v>0</v>
       </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-100</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7874,8 +8122,8 @@
       <c r="J101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -7934,90 +8182,96 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>9100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OBLG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OBLG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="92">
   <si>
     <t>OBLG</t>
   </si>
@@ -656,136 +656,140 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -802,79 +806,82 @@
         <v>600</v>
       </c>
       <c r="H8" s="3">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="I8" s="3">
         <v>900</v>
       </c>
       <c r="J8" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="K8" s="3">
         <v>1000</v>
       </c>
       <c r="L8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M8" s="3">
         <v>1400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5400</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>2400</v>
       </c>
       <c r="Z8" s="3">
         <v>2400</v>
       </c>
       <c r="AA8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AB8" s="3">
         <v>2600</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>2900</v>
       </c>
       <c r="AC8" s="3">
         <v>2900</v>
       </c>
       <c r="AD8" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AE8" s="3">
         <v>3300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -882,93 +889,96 @@
         <v>400</v>
       </c>
       <c r="E9" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F9" s="3">
         <v>500</v>
       </c>
       <c r="G9" s="3">
+        <v>500</v>
+      </c>
+      <c r="H9" s="3">
         <v>600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>600</v>
-      </c>
-      <c r="J9" s="3">
-        <v>800</v>
       </c>
       <c r="K9" s="3">
         <v>800</v>
       </c>
       <c r="L9" s="3">
+        <v>800</v>
+      </c>
+      <c r="M9" s="3">
         <v>1100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1300</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>1200</v>
       </c>
       <c r="R9" s="3">
         <v>1200</v>
       </c>
       <c r="S9" s="3">
+        <v>1200</v>
+      </c>
+      <c r="T9" s="3">
         <v>1300</v>
-      </c>
-      <c r="T9" s="3">
-        <v>1600</v>
       </c>
       <c r="U9" s="3">
         <v>1600</v>
       </c>
       <c r="V9" s="3">
+        <v>1600</v>
+      </c>
+      <c r="W9" s="3">
         <v>4100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2500</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>1600</v>
       </c>
       <c r="Z9" s="3">
         <v>1600</v>
       </c>
       <c r="AA9" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="AB9" s="3">
         <v>1700</v>
       </c>
       <c r="AC9" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AD9" s="3">
         <v>1800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E10" s="3">
         <v>100</v>
@@ -977,82 +987,85 @@
         <v>100</v>
       </c>
       <c r="G10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
         <v>300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>100</v>
-      </c>
-      <c r="K10" s="3">
-        <v>300</v>
       </c>
       <c r="L10" s="3">
         <v>300</v>
       </c>
       <c r="M10" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="N10" s="3">
         <v>400</v>
       </c>
       <c r="O10" s="3">
+        <v>400</v>
+      </c>
+      <c r="P10" s="3">
         <v>500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4000</v>
-      </c>
-      <c r="W10" s="3">
-        <v>2900</v>
       </c>
       <c r="X10" s="3">
         <v>2900</v>
       </c>
       <c r="Y10" s="3">
-        <v>800</v>
+        <v>2900</v>
       </c>
       <c r="Z10" s="3">
         <v>800</v>
       </c>
       <c r="AA10" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB10" s="3">
         <v>900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1100</v>
-      </c>
-      <c r="AD10" s="3">
-        <v>1400</v>
       </c>
       <c r="AE10" s="3">
         <v>1400</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1096,13 +1110,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G12" s="3">
         <v>100</v>
       </c>
       <c r="H12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I12" s="3">
         <v>0</v>
@@ -1114,46 +1128,46 @@
         <v>0</v>
       </c>
       <c r="L12" s="3">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3">
         <v>100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1400</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>200</v>
       </c>
       <c r="Z12" s="3">
         <v>200</v>
@@ -1171,10 +1185,13 @@
         <v>200</v>
       </c>
       <c r="AE12" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF12" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1262,8 +1279,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1279,85 +1299,88 @@
       <c r="G14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="3">
         <v>300</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>5200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>6900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1100</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-2200</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>-2600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>100</v>
-      </c>
-      <c r="V14" s="3">
-        <v>600</v>
       </c>
       <c r="W14" s="3">
         <v>600</v>
       </c>
       <c r="X14" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y14" s="3">
         <v>1800</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>500</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>1800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
         <v>100</v>
@@ -1384,7 +1407,7 @@
         <v>100</v>
       </c>
       <c r="M15" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="N15" s="3">
         <v>600</v>
@@ -1396,7 +1419,7 @@
         <v>600</v>
       </c>
       <c r="Q15" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="R15" s="3">
         <v>700</v>
@@ -1408,22 +1431,22 @@
         <v>700</v>
       </c>
       <c r="U15" s="3">
+        <v>700</v>
+      </c>
+      <c r="V15" s="3">
         <v>800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>100</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>200</v>
       </c>
       <c r="AA15" s="3">
         <v>200</v>
@@ -1440,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>14400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-9100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-6300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-5500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1681,8 +1714,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1695,27 +1729,27 @@
       <c r="F20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
+      <c r="G20" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-400</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>100</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1729,11 +1763,11 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>300</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1747,11 +1781,11 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
@@ -1759,108 +1793,114 @@
         <v>0</v>
       </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-200</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1000</v>
       </c>
-      <c r="H21" s="3">
-        <v>-1100</v>
-      </c>
       <c r="I21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J21" s="3">
         <v>-800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1000</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-1100</v>
       </c>
       <c r="L21" s="3">
         <v>-1100</v>
       </c>
       <c r="M21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="N21" s="3">
         <v>-6600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-8400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q21" s="3">
-        <v>0</v>
-      </c>
       <c r="R21" s="3">
+        <v>0</v>
+      </c>
+      <c r="S21" s="3">
         <v>-1500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-4700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1876,26 +1916,26 @@
       <c r="G22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>17</v>
+      <c r="H22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1916,19 +1956,19 @@
         <v>0</v>
       </c>
       <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
         <v>100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>200</v>
-      </c>
-      <c r="W22" s="3">
-        <v>100</v>
       </c>
       <c r="X22" s="3">
         <v>100</v>
       </c>
       <c r="Y22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
@@ -1936,135 +1976,141 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
       </c>
       <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-900</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-1000</v>
       </c>
       <c r="F23" s="3">
         <v>-1000</v>
       </c>
       <c r="G23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H23" s="3">
         <v>-1100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1000</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-1200</v>
       </c>
       <c r="L23" s="3">
         <v>-1200</v>
       </c>
       <c r="M23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="N23" s="3">
         <v>-7200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-9000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-6500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-5600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>17</v>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -2079,11 +2125,11 @@
         <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
@@ -2091,11 +2137,11 @@
         <v>0</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="V24" s="3" t="s">
         <v>17</v>
       </c>
@@ -2114,8 +2160,8 @@
       <c r="AA24" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
+      <c r="AB24" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="AC24" s="3">
         <v>0</v>
@@ -2126,8 +2172,11 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-900</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-1000</v>
       </c>
       <c r="F26" s="3">
         <v>-1000</v>
       </c>
       <c r="G26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H26" s="3">
         <v>-1100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1000</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-1200</v>
       </c>
       <c r="L26" s="3">
         <v>-1200</v>
       </c>
       <c r="M26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="N26" s="3">
         <v>-7200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-6500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-5600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-10000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1900</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-1200</v>
       </c>
       <c r="L27" s="3">
         <v>-1200</v>
       </c>
       <c r="M27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="N27" s="3">
         <v>-7200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-6500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-5700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,8 +2816,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2763,27 +2833,27 @@
       <c r="F32" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
+      <c r="G32" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K32" s="3">
+        <v>400</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J32" s="3">
-        <v>400</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -2797,11 +2867,11 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-300</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -2815,11 +2885,11 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
@@ -2827,108 +2897,114 @@
         <v>0</v>
       </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>200</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-900</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-1000</v>
       </c>
       <c r="F33" s="3">
         <v>-1000</v>
       </c>
       <c r="G33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H33" s="3">
         <v>-1100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1000</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-1200</v>
       </c>
       <c r="L33" s="3">
         <v>-1200</v>
       </c>
       <c r="M33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="N33" s="3">
         <v>-7200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-6500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-5700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-900</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-1000</v>
       </c>
       <c r="F35" s="3">
         <v>-1000</v>
       </c>
       <c r="G35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H35" s="3">
         <v>-1100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1000</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-1200</v>
       </c>
       <c r="L35" s="3">
         <v>-1200</v>
       </c>
       <c r="M35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="N35" s="3">
         <v>-7200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-6500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-5700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,97 +3351,101 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E41" s="3">
         <v>5000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>13000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,17 +3533,20 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>100</v>
+      </c>
+      <c r="E43" s="3">
         <v>200</v>
       </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
       <c r="F43" s="3">
         <v>0</v>
       </c>
@@ -3461,16 +3554,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="3">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3">
         <v>400</v>
-      </c>
-      <c r="I43" s="3">
-        <v>200</v>
       </c>
       <c r="J43" s="3">
         <v>200</v>
       </c>
       <c r="K43" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="L43" s="3">
         <v>400</v>
@@ -3479,46 +3572,46 @@
         <v>400</v>
       </c>
       <c r="N43" s="3">
+        <v>400</v>
+      </c>
+      <c r="O43" s="3">
         <v>500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1500</v>
-      </c>
-      <c r="AA43" s="3">
-        <v>1400</v>
       </c>
       <c r="AB43" s="3">
         <v>1400</v>
@@ -3527,13 +3620,16 @@
         <v>1400</v>
       </c>
       <c r="AD43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AE43" s="3">
         <v>1500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3541,7 +3637,7 @@
         <v>17</v>
       </c>
       <c r="E44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F44" s="3">
         <v>100</v>
@@ -3550,59 +3646,59 @@
         <v>100</v>
       </c>
       <c r="H44" s="3">
+        <v>100</v>
+      </c>
+      <c r="I44" s="3">
         <v>200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1800</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="Z44" s="3" t="s">
         <v>17</v>
       </c>
@@ -3621,8 +3717,11 @@
       <c r="AE44" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3638,8 +3737,8 @@
       <c r="G45" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H45" s="3">
-        <v>200</v>
+      <c r="H45" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>17</v>
@@ -3650,56 +3749,56 @@
       <c r="K45" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M45" s="3">
         <v>600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1100</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>1500</v>
       </c>
       <c r="R45" s="3">
         <v>1500</v>
       </c>
       <c r="S45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="T45" s="3">
         <v>1200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>600</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>500</v>
       </c>
       <c r="AC45" s="3">
         <v>500</v>
@@ -3708,99 +3807,105 @@
         <v>500</v>
       </c>
       <c r="AE45" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF45" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E46" s="3">
         <v>5300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>15400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>17600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>10000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>8800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>9900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3828,8 +3933,8 @@
       <c r="K47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3888,8 +3993,11 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3905,14 +4013,14 @@
       <c r="G48" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H48" s="3">
-        <v>0</v>
+      <c r="H48" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="I48" s="3">
         <v>0</v>
       </c>
       <c r="J48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3">
         <v>100</v>
@@ -3921,55 +4029,55 @@
         <v>100</v>
       </c>
       <c r="M48" s="3">
+        <v>100</v>
+      </c>
+      <c r="N48" s="3">
         <v>200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>700</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>1000</v>
       </c>
       <c r="AD48" s="3">
         <v>1000</v>
@@ -3977,8 +4085,11 @@
       <c r="AE48" s="3">
         <v>1000</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3998,76 +4109,79 @@
         <v>0</v>
       </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>13200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>14900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>15500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>16300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>16900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>17500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>18100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>18700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>19300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>20500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2800</v>
-      </c>
-      <c r="AA49" s="3">
-        <v>3300</v>
       </c>
       <c r="AB49" s="3">
         <v>3300</v>
       </c>
       <c r="AC49" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AD49" s="3">
         <v>5100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>6100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,8 +4361,11 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4277,13 +4397,13 @@
         <v>0</v>
       </c>
       <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
         <v>100</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
-      </c>
       <c r="O52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P52" s="3">
         <v>100</v>
@@ -4298,10 +4418,10 @@
         <v>100</v>
       </c>
       <c r="T52" s="3">
+        <v>100</v>
+      </c>
+      <c r="U52" s="3">
         <v>200</v>
-      </c>
-      <c r="U52" s="3">
-        <v>100</v>
       </c>
       <c r="V52" s="3">
         <v>100</v>
@@ -4313,16 +4433,16 @@
         <v>100</v>
       </c>
       <c r="Y52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA52" s="3">
         <v>100</v>
       </c>
       <c r="AB52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC52" s="3">
         <v>0</v>
@@ -4333,8 +4453,11 @@
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4545,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E54" s="3">
         <v>5300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>24200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>28600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>31700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>34900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>26700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>29100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>27200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>29300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>32000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>34900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>8000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>10500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>11900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>13800</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,8 +4707,9 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4592,82 +4723,85 @@
         <v>100</v>
       </c>
       <c r="G57" s="3">
+        <v>100</v>
+      </c>
+      <c r="H57" s="3">
         <v>400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>200</v>
-      </c>
-      <c r="I57" s="3">
-        <v>100</v>
       </c>
       <c r="J57" s="3">
         <v>100</v>
       </c>
       <c r="K57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L57" s="3">
         <v>200</v>
       </c>
       <c r="M57" s="3">
+        <v>200</v>
+      </c>
+      <c r="N57" s="3">
         <v>400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>300</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>500</v>
       </c>
       <c r="R57" s="3">
         <v>500</v>
       </c>
       <c r="S57" s="3">
+        <v>500</v>
+      </c>
+      <c r="T57" s="3">
         <v>1100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>300</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>200</v>
       </c>
       <c r="AB57" s="3">
         <v>200</v>
       </c>
       <c r="AC57" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD57" s="3">
         <v>400</v>
-      </c>
-      <c r="AD57" s="3">
-        <v>300</v>
       </c>
       <c r="AE57" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4690,13 +4824,13 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3">
         <v>100</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -4717,34 +4851,34 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>2400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2700</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>17</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
+      <c r="AB58" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="AC58" s="3">
         <v>0</v>
@@ -4755,8 +4889,11 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4764,177 +4901,183 @@
         <v>0</v>
       </c>
       <c r="E59" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F59" s="3">
         <v>200</v>
       </c>
       <c r="G59" s="3">
+        <v>200</v>
+      </c>
+      <c r="H59" s="3">
         <v>300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>400</v>
-      </c>
-      <c r="I59" s="3">
-        <v>600</v>
       </c>
       <c r="J59" s="3">
         <v>600</v>
       </c>
       <c r="K59" s="3">
+        <v>600</v>
+      </c>
+      <c r="L59" s="3">
         <v>700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1700</v>
-      </c>
-      <c r="M59" s="3">
-        <v>2000</v>
       </c>
       <c r="N59" s="3">
         <v>2000</v>
       </c>
       <c r="O59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P59" s="3">
         <v>2300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>900</v>
-      </c>
-      <c r="AC59" s="3">
-        <v>700</v>
       </c>
       <c r="AD59" s="3">
         <v>700</v>
       </c>
       <c r="AE59" s="3">
+        <v>700</v>
+      </c>
+      <c r="AF59" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="E60" s="3">
         <v>1300</v>
       </c>
       <c r="F60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G60" s="3">
         <v>1200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1900</v>
-      </c>
-      <c r="M60" s="3">
-        <v>2400</v>
       </c>
       <c r="N60" s="3">
         <v>2400</v>
       </c>
       <c r="O60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="P60" s="3">
         <v>2800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>8300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1400</v>
-      </c>
-      <c r="AB60" s="3">
-        <v>1100</v>
       </c>
       <c r="AC60" s="3">
         <v>1100</v>
       </c>
       <c r="AD60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AE60" s="3">
         <v>1000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4981,29 +5124,29 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>2400</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2800</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -5022,8 +5165,11 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5051,20 +5197,20 @@
       <c r="K62" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M62" s="3">
         <v>100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>500</v>
-      </c>
-      <c r="P62" s="3">
-        <v>600</v>
       </c>
       <c r="Q62" s="3">
         <v>600</v>
@@ -5073,26 +5219,26 @@
         <v>600</v>
       </c>
       <c r="S62" s="3">
+        <v>600</v>
+      </c>
+      <c r="T62" s="3">
         <v>1000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2000</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>17</v>
       </c>
@@ -5111,8 +5257,11 @@
       <c r="AE62" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,13 +5533,16 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="E66" s="3">
         <v>1300</v>
@@ -5393,82 +5551,85 @@
         <v>1300</v>
       </c>
       <c r="G66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H66" s="3">
         <v>1500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1400</v>
-      </c>
-      <c r="I66" s="3">
-        <v>1300</v>
       </c>
       <c r="J66" s="3">
         <v>1300</v>
       </c>
       <c r="K66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L66" s="3">
         <v>2400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2000</v>
-      </c>
-      <c r="M66" s="3">
-        <v>2600</v>
       </c>
       <c r="N66" s="3">
         <v>2600</v>
       </c>
       <c r="O66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="P66" s="3">
         <v>3300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7100</v>
-      </c>
-      <c r="U66" s="3">
-        <v>13900</v>
       </c>
       <c r="V66" s="3">
         <v>13900</v>
       </c>
       <c r="W66" s="3">
+        <v>13900</v>
+      </c>
+      <c r="X66" s="3">
         <v>13200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>13100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1400</v>
-      </c>
-      <c r="AB66" s="3">
-        <v>1100</v>
       </c>
       <c r="AC66" s="3">
         <v>1100</v>
       </c>
       <c r="AD66" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AE66" s="3">
         <v>1000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6027,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-232900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-232300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-231400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-230400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-229400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-228200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-227000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-226100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-225100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-223800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-222600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-215500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-206400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-201900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-199200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-198500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-196300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-192900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-194000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-191900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-188600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-185400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-179800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-179100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-178300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-177700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-174900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-173500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-171800</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6395,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E76" s="3">
         <v>4000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>25500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>28100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>28300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>18900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>22100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>18800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>21800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>9500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>10900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-900</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-1000</v>
       </c>
       <c r="F81" s="3">
         <v>-1000</v>
       </c>
       <c r="G81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H81" s="3">
         <v>-1100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1000</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-1200</v>
       </c>
       <c r="L81" s="3">
         <v>-1200</v>
       </c>
       <c r="M81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="N81" s="3">
         <v>-7200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-6500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-5700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6623,8 +6822,8 @@
       <c r="G83" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
+      <c r="H83" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="I83" s="3">
         <v>0</v>
@@ -6636,10 +6835,10 @@
         <v>0</v>
       </c>
       <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
         <v>100</v>
-      </c>
-      <c r="M83" s="3">
-        <v>600</v>
       </c>
       <c r="N83" s="3">
         <v>600</v>
@@ -6651,7 +6850,7 @@
         <v>600</v>
       </c>
       <c r="Q83" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="R83" s="3">
         <v>700</v>
@@ -6663,22 +6862,22 @@
         <v>700</v>
       </c>
       <c r="U83" s="3">
+        <v>700</v>
+      </c>
+      <c r="V83" s="3">
         <v>800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>100</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>200</v>
       </c>
       <c r="AA83" s="3">
         <v>200</v>
@@ -6695,8 +6894,11 @@
       <c r="AE83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7354,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-900</v>
+        <v>-700</v>
       </c>
       <c r="E89" s="3">
         <v>-900</v>
       </c>
       <c r="F89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G89" s="3">
         <v>-1000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-2500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,8 +7482,9 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7291,8 +7512,8 @@
       <c r="K91" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -7324,11 +7545,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
@@ -7343,16 +7564,19 @@
         <v>0</v>
       </c>
       <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-200</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,8 +7756,11 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7558,8 +7788,8 @@
       <c r="K94" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -7595,11 +7825,11 @@
         <v>0</v>
       </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>2200</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
         <v>0</v>
       </c>
@@ -7610,16 +7840,19 @@
         <v>0</v>
       </c>
       <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-200</v>
       </c>
-      <c r="AE94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7680,8 +7914,8 @@
       <c r="K96" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,77 +8250,80 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1500</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>4500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1500</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>17</v>
+      <c r="N100" s="3">
+        <v>0</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
+      <c r="P100" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>11500</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>4900</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>2400</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>3800</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
         <v>0</v>
       </c>
@@ -8088,16 +8334,19 @@
         <v>0</v>
       </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-100</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8125,8 +8374,8 @@
       <c r="K101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -8185,93 +8434,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>9100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OBLG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OBLG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="92">
   <si>
     <t>OBLG</t>
   </si>
@@ -656,140 +656,144 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -809,79 +813,82 @@
         <v>600</v>
       </c>
       <c r="I8" s="3">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="J8" s="3">
         <v>900</v>
       </c>
       <c r="K8" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="L8" s="3">
         <v>1000</v>
       </c>
       <c r="M8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N8" s="3">
         <v>1400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5400</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>2400</v>
       </c>
       <c r="AA8" s="3">
         <v>2400</v>
       </c>
       <c r="AB8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AC8" s="3">
         <v>2600</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>2900</v>
       </c>
       <c r="AD8" s="3">
         <v>2900</v>
       </c>
       <c r="AE8" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AF8" s="3">
         <v>3300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -892,88 +899,91 @@
         <v>400</v>
       </c>
       <c r="F9" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G9" s="3">
         <v>500</v>
       </c>
       <c r="H9" s="3">
+        <v>500</v>
+      </c>
+      <c r="I9" s="3">
         <v>600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>600</v>
-      </c>
-      <c r="K9" s="3">
-        <v>800</v>
       </c>
       <c r="L9" s="3">
         <v>800</v>
       </c>
       <c r="M9" s="3">
+        <v>800</v>
+      </c>
+      <c r="N9" s="3">
         <v>1100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1300</v>
-      </c>
-      <c r="R9" s="3">
-        <v>1200</v>
       </c>
       <c r="S9" s="3">
         <v>1200</v>
       </c>
       <c r="T9" s="3">
+        <v>1200</v>
+      </c>
+      <c r="U9" s="3">
         <v>1300</v>
-      </c>
-      <c r="U9" s="3">
-        <v>1600</v>
       </c>
       <c r="V9" s="3">
         <v>1600</v>
       </c>
       <c r="W9" s="3">
+        <v>1600</v>
+      </c>
+      <c r="X9" s="3">
         <v>4100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2500</v>
-      </c>
-      <c r="Z9" s="3">
-        <v>1600</v>
       </c>
       <c r="AA9" s="3">
         <v>1600</v>
       </c>
       <c r="AB9" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="AC9" s="3">
         <v>1700</v>
       </c>
       <c r="AD9" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AE9" s="3">
         <v>1800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -981,7 +991,7 @@
         <v>200</v>
       </c>
       <c r="E10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F10" s="3">
         <v>100</v>
@@ -990,82 +1000,85 @@
         <v>100</v>
       </c>
       <c r="H10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
         <v>300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>100</v>
-      </c>
-      <c r="L10" s="3">
-        <v>300</v>
       </c>
       <c r="M10" s="3">
         <v>300</v>
       </c>
       <c r="N10" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="O10" s="3">
         <v>400</v>
       </c>
       <c r="P10" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q10" s="3">
         <v>500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>4000</v>
-      </c>
-      <c r="X10" s="3">
-        <v>2900</v>
       </c>
       <c r="Y10" s="3">
         <v>2900</v>
       </c>
       <c r="Z10" s="3">
-        <v>800</v>
+        <v>2900</v>
       </c>
       <c r="AA10" s="3">
         <v>800</v>
       </c>
       <c r="AB10" s="3">
+        <v>800</v>
+      </c>
+      <c r="AC10" s="3">
         <v>900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1100</v>
-      </c>
-      <c r="AE10" s="3">
-        <v>1400</v>
       </c>
       <c r="AF10" s="3">
         <v>1400</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1111,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1113,13 +1127,13 @@
         <v>0</v>
       </c>
       <c r="G12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H12" s="3">
         <v>100</v>
       </c>
       <c r="I12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12" s="3">
         <v>0</v>
@@ -1131,46 +1145,46 @@
         <v>0</v>
       </c>
       <c r="M12" s="3">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3">
         <v>100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>2300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1400</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>200</v>
       </c>
       <c r="AA12" s="3">
         <v>200</v>
@@ -1188,10 +1202,13 @@
         <v>200</v>
       </c>
       <c r="AF12" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG12" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1282,8 +1299,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,80 +1322,83 @@
       <c r="H14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="3">
         <v>300</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>5200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>6900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1100</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-2200</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>-2600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>100</v>
-      </c>
-      <c r="W14" s="3">
-        <v>600</v>
       </c>
       <c r="X14" s="3">
         <v>600</v>
       </c>
       <c r="Y14" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z14" s="3">
         <v>1800</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>500</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>1800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>1500</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1383,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
         <v>100</v>
@@ -1410,7 +1433,7 @@
         <v>100</v>
       </c>
       <c r="N15" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="O15" s="3">
         <v>600</v>
@@ -1422,7 +1445,7 @@
         <v>600</v>
       </c>
       <c r="R15" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="S15" s="3">
         <v>700</v>
@@ -1434,22 +1457,22 @@
         <v>700</v>
       </c>
       <c r="V15" s="3">
+        <v>700</v>
+      </c>
+      <c r="W15" s="3">
         <v>800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>100</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>200</v>
       </c>
       <c r="AB15" s="3">
         <v>200</v>
@@ -1466,8 +1489,11 @@
       <c r="AF15" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,8 +1523,9 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
@@ -1506,91 +1533,94 @@
         <v>1300</v>
       </c>
       <c r="E17" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F17" s="3">
         <v>1500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>14400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>10900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
@@ -1598,91 +1628,94 @@
         <v>-700</v>
       </c>
       <c r="E18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-9100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-6300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-5500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1715,13 +1748,14 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>17</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>17</v>
@@ -1732,8 +1766,8 @@
       <c r="G20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
+      <c r="H20" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>17</v>
@@ -1741,18 +1775,18 @@
       <c r="J20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1766,11 +1800,11 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>300</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
@@ -1784,11 +1818,11 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-100</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
@@ -1796,19 +1830,22 @@
         <v>0</v>
       </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-200</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -1816,91 +1853,94 @@
         <v>-700</v>
       </c>
       <c r="E21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F21" s="3">
         <v>-800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L21" s="3">
         <v>-1000</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-900</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-800</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-1100</v>
       </c>
       <c r="M21" s="3">
         <v>-1100</v>
       </c>
       <c r="N21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="O21" s="3">
         <v>-6600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-8400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2200</v>
       </c>
-      <c r="R21" s="3">
-        <v>0</v>
-      </c>
       <c r="S21" s="3">
+        <v>0</v>
+      </c>
+      <c r="T21" s="3">
         <v>-1500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-4700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1919,26 +1959,26 @@
       <c r="H22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>17</v>
+      <c r="I22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1959,19 +1999,19 @@
         <v>0</v>
       </c>
       <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
         <v>100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>200</v>
-      </c>
-      <c r="X22" s="3">
-        <v>100</v>
       </c>
       <c r="Y22" s="3">
         <v>100</v>
       </c>
       <c r="Z22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
@@ -1979,141 +2019,147 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>0</v>
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="AE22" s="3">
         <v>0</v>
       </c>
       <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-900</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-1000</v>
       </c>
       <c r="G23" s="3">
         <v>-1000</v>
       </c>
       <c r="H23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I23" s="3">
         <v>-1100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1000</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-1200</v>
       </c>
       <c r="M23" s="3">
         <v>-1200</v>
       </c>
       <c r="N23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="O23" s="3">
         <v>-7200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-9000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-6500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-5600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>17</v>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -2128,11 +2174,11 @@
         <v>0</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
@@ -2140,11 +2186,11 @@
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="W24" s="3" t="s">
         <v>17</v>
       </c>
@@ -2163,8 +2209,8 @@
       <c r="AB24" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
+      <c r="AC24" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="AD24" s="3">
         <v>0</v>
@@ -2175,8 +2221,11 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2316,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-900</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-1000</v>
       </c>
       <c r="G26" s="3">
         <v>-1000</v>
       </c>
       <c r="H26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I26" s="3">
         <v>-1100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1000</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-1200</v>
       </c>
       <c r="M26" s="3">
         <v>-1200</v>
       </c>
       <c r="N26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="O26" s="3">
         <v>-7200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-6500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-5600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1900</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-1200</v>
       </c>
       <c r="M27" s="3">
         <v>-1200</v>
       </c>
       <c r="N27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="O27" s="3">
         <v>-7200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-6500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-5700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,13 +2886,16 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>17</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>17</v>
@@ -2836,8 +2906,8 @@
       <c r="G32" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
+      <c r="H32" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>17</v>
@@ -2845,18 +2915,18 @@
       <c r="J32" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -2870,11 +2940,11 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-300</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
@@ -2888,11 +2958,11 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>100</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
@@ -2900,111 +2970,117 @@
         <v>0</v>
       </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>200</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
         <v>0</v>
       </c>
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-900</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-1000</v>
       </c>
       <c r="G33" s="3">
         <v>-1000</v>
       </c>
       <c r="H33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I33" s="3">
         <v>-1100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1000</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-1200</v>
       </c>
       <c r="M33" s="3">
         <v>-1200</v>
       </c>
       <c r="N33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="O33" s="3">
         <v>-7200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-6500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-5700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3171,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-900</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-1000</v>
       </c>
       <c r="G35" s="3">
         <v>-1000</v>
       </c>
       <c r="H35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I35" s="3">
         <v>-1100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1000</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-1200</v>
       </c>
       <c r="M35" s="3">
         <v>-1200</v>
       </c>
       <c r="N35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="O35" s="3">
         <v>-7200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-6500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-5700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3438,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E41" s="3">
         <v>4300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>13000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,20 +3626,23 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
         <v>100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>200</v>
       </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
       <c r="G43" s="3">
         <v>0</v>
       </c>
@@ -3557,16 +3650,16 @@
         <v>0</v>
       </c>
       <c r="I43" s="3">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3">
         <v>400</v>
-      </c>
-      <c r="J43" s="3">
-        <v>200</v>
       </c>
       <c r="K43" s="3">
         <v>200</v>
       </c>
       <c r="L43" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="M43" s="3">
         <v>400</v>
@@ -3575,46 +3668,46 @@
         <v>400</v>
       </c>
       <c r="O43" s="3">
+        <v>400</v>
+      </c>
+      <c r="P43" s="3">
         <v>500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1500</v>
-      </c>
-      <c r="AB43" s="3">
-        <v>1400</v>
       </c>
       <c r="AC43" s="3">
         <v>1400</v>
@@ -3623,24 +3716,27 @@
         <v>1400</v>
       </c>
       <c r="AE43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AF43" s="3">
         <v>1500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E44" s="3">
-        <v>0</v>
+      <c r="E44" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="F44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G44" s="3">
         <v>100</v>
@@ -3649,59 +3745,59 @@
         <v>100</v>
       </c>
       <c r="I44" s="3">
+        <v>100</v>
+      </c>
+      <c r="J44" s="3">
         <v>200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1800</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="AA44" s="3" t="s">
         <v>17</v>
       </c>
@@ -3720,13 +3816,16 @@
       <c r="AF44" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>17</v>
+      <c r="D45" s="3">
+        <v>1700</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>17</v>
@@ -3752,56 +3851,56 @@
       <c r="L45" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N45" s="3">
         <v>600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1100</v>
-      </c>
-      <c r="R45" s="3">
-        <v>1500</v>
       </c>
       <c r="S45" s="3">
         <v>1500</v>
       </c>
       <c r="T45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="U45" s="3">
         <v>1200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>600</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>500</v>
       </c>
       <c r="AD45" s="3">
         <v>500</v>
@@ -3810,102 +3909,108 @@
         <v>500</v>
       </c>
       <c r="AF45" s="3">
+        <v>500</v>
+      </c>
+      <c r="AG45" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E46" s="3">
         <v>4800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>12800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>15400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>17600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>8400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>10000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>8800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>9900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3936,8 +4041,8 @@
       <c r="L47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3996,8 +4101,11 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4016,14 +4124,14 @@
       <c r="H48" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I48" s="3">
-        <v>0</v>
+      <c r="I48" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="J48" s="3">
         <v>0</v>
       </c>
       <c r="K48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3">
         <v>100</v>
@@ -4032,55 +4140,55 @@
         <v>100</v>
       </c>
       <c r="N48" s="3">
+        <v>100</v>
+      </c>
+      <c r="O48" s="3">
         <v>200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>700</v>
-      </c>
-      <c r="AD48" s="3">
-        <v>1000</v>
       </c>
       <c r="AE48" s="3">
         <v>1000</v>
@@ -4088,8 +4196,11 @@
       <c r="AF48" s="3">
         <v>1000</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4112,76 +4223,79 @@
         <v>0</v>
       </c>
       <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>6400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>13200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>14900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>15500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>16300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>16900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>17500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>18100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>18700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>19300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>20500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2800</v>
-      </c>
-      <c r="AB49" s="3">
-        <v>3300</v>
       </c>
       <c r="AC49" s="3">
         <v>3300</v>
       </c>
       <c r="AD49" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AE49" s="3">
         <v>5100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>6100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,8 +4481,11 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4400,13 +4520,13 @@
         <v>0</v>
       </c>
       <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
         <v>100</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
       <c r="P52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="3">
         <v>100</v>
@@ -4421,10 +4541,10 @@
         <v>100</v>
       </c>
       <c r="U52" s="3">
+        <v>100</v>
+      </c>
+      <c r="V52" s="3">
         <v>200</v>
-      </c>
-      <c r="V52" s="3">
-        <v>100</v>
       </c>
       <c r="W52" s="3">
         <v>100</v>
@@ -4436,16 +4556,16 @@
         <v>100</v>
       </c>
       <c r="Z52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB52" s="3">
         <v>100</v>
       </c>
       <c r="AC52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD52" s="3">
         <v>0</v>
@@ -4456,8 +4576,11 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4671,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E54" s="3">
         <v>4800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>24200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>28600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>31700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>34900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>26700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>29100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>27200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>29300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>32000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>34900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>8000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>10500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>11900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>13800</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,8 +4838,9 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4726,82 +4857,85 @@
         <v>100</v>
       </c>
       <c r="H57" s="3">
+        <v>100</v>
+      </c>
+      <c r="I57" s="3">
         <v>400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>200</v>
-      </c>
-      <c r="J57" s="3">
-        <v>100</v>
       </c>
       <c r="K57" s="3">
         <v>100</v>
       </c>
       <c r="L57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M57" s="3">
         <v>200</v>
       </c>
       <c r="N57" s="3">
+        <v>200</v>
+      </c>
+      <c r="O57" s="3">
         <v>400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>300</v>
-      </c>
-      <c r="R57" s="3">
-        <v>500</v>
       </c>
       <c r="S57" s="3">
         <v>500</v>
       </c>
       <c r="T57" s="3">
+        <v>500</v>
+      </c>
+      <c r="U57" s="3">
         <v>1100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>300</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>200</v>
       </c>
       <c r="AC57" s="3">
         <v>200</v>
       </c>
       <c r="AD57" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE57" s="3">
         <v>400</v>
-      </c>
-      <c r="AE57" s="3">
-        <v>300</v>
       </c>
       <c r="AF57" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4827,13 +4961,13 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L58" s="3">
         <v>100</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -4854,34 +4988,34 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>2400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2700</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="AA58" s="3" t="s">
         <v>17</v>
       </c>
       <c r="AB58" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
+      <c r="AC58" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="AD58" s="3">
         <v>0</v>
@@ -4892,192 +5026,201 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E59" s="3">
+        <v>400</v>
+      </c>
+      <c r="F59" s="3">
         <v>300</v>
-      </c>
-      <c r="F59" s="3">
-        <v>200</v>
       </c>
       <c r="G59" s="3">
         <v>200</v>
       </c>
       <c r="H59" s="3">
+        <v>200</v>
+      </c>
+      <c r="I59" s="3">
         <v>300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>400</v>
-      </c>
-      <c r="J59" s="3">
-        <v>600</v>
       </c>
       <c r="K59" s="3">
         <v>600</v>
       </c>
       <c r="L59" s="3">
+        <v>600</v>
+      </c>
+      <c r="M59" s="3">
         <v>700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1700</v>
-      </c>
-      <c r="N59" s="3">
-        <v>2000</v>
       </c>
       <c r="O59" s="3">
         <v>2000</v>
       </c>
       <c r="P59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Q59" s="3">
         <v>2300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>900</v>
-      </c>
-      <c r="AD59" s="3">
-        <v>700</v>
       </c>
       <c r="AE59" s="3">
         <v>700</v>
       </c>
       <c r="AF59" s="3">
+        <v>700</v>
+      </c>
+      <c r="AG59" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E60" s="3">
         <v>1400</v>
-      </c>
-      <c r="E60" s="3">
-        <v>1300</v>
       </c>
       <c r="F60" s="3">
         <v>1300</v>
       </c>
       <c r="G60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H60" s="3">
         <v>1200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1900</v>
-      </c>
-      <c r="N60" s="3">
-        <v>2400</v>
       </c>
       <c r="O60" s="3">
         <v>2400</v>
       </c>
       <c r="P60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Q60" s="3">
         <v>2800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>8500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>8300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1400</v>
-      </c>
-      <c r="AC60" s="3">
-        <v>1100</v>
       </c>
       <c r="AD60" s="3">
         <v>1100</v>
       </c>
       <c r="AE60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AF60" s="3">
         <v>1000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5127,29 +5270,29 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>2400</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2800</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -5168,8 +5311,11 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5200,20 +5346,20 @@
       <c r="L62" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N62" s="3">
         <v>100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>500</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>600</v>
       </c>
       <c r="R62" s="3">
         <v>600</v>
@@ -5222,26 +5368,26 @@
         <v>600</v>
       </c>
       <c r="T62" s="3">
+        <v>600</v>
+      </c>
+      <c r="U62" s="3">
         <v>1000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2000</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>17</v>
       </c>
@@ -5260,8 +5406,11 @@
       <c r="AF62" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,16 +5691,19 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E66" s="3">
         <v>1400</v>
-      </c>
-      <c r="E66" s="3">
-        <v>1300</v>
       </c>
       <c r="F66" s="3">
         <v>1300</v>
@@ -5554,82 +5712,85 @@
         <v>1300</v>
       </c>
       <c r="H66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I66" s="3">
         <v>1500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1400</v>
-      </c>
-      <c r="J66" s="3">
-        <v>1300</v>
       </c>
       <c r="K66" s="3">
         <v>1300</v>
       </c>
       <c r="L66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="M66" s="3">
         <v>2400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2000</v>
-      </c>
-      <c r="N66" s="3">
-        <v>2600</v>
       </c>
       <c r="O66" s="3">
         <v>2600</v>
       </c>
       <c r="P66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="Q66" s="3">
         <v>3300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7100</v>
-      </c>
-      <c r="V66" s="3">
-        <v>13900</v>
       </c>
       <c r="W66" s="3">
         <v>13900</v>
       </c>
       <c r="X66" s="3">
+        <v>13900</v>
+      </c>
+      <c r="Y66" s="3">
         <v>13200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>13100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1400</v>
-      </c>
-      <c r="AC66" s="3">
-        <v>1100</v>
       </c>
       <c r="AD66" s="3">
         <v>1100</v>
       </c>
       <c r="AE66" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AF66" s="3">
         <v>1000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6201,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-233600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-232900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-232300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-231400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-230400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-229400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-228200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-227000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-226100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-225100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-223800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-222600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-215500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-206400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-201900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-199200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-198500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-196300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-192900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-194000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-191900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-188600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-185400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-179800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-179100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-178300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-177700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-174900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-173500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-171800</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6581,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E76" s="3">
         <v>3400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>20900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>25500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>28100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>28300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>18900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>22100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>18800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>21800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>9500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>10900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6771,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-900</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-1000</v>
       </c>
       <c r="G81" s="3">
         <v>-1000</v>
       </c>
       <c r="H81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I81" s="3">
         <v>-1100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1000</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-1200</v>
       </c>
       <c r="M81" s="3">
         <v>-1200</v>
       </c>
       <c r="N81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="O81" s="3">
         <v>-7200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-6500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-5700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7003,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6825,8 +7024,8 @@
       <c r="H83" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
+      <c r="I83" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="J83" s="3">
         <v>0</v>
@@ -6838,10 +7037,10 @@
         <v>0</v>
       </c>
       <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
         <v>100</v>
-      </c>
-      <c r="N83" s="3">
-        <v>600</v>
       </c>
       <c r="O83" s="3">
         <v>600</v>
@@ -6853,7 +7052,7 @@
         <v>600</v>
       </c>
       <c r="R83" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="S83" s="3">
         <v>700</v>
@@ -6865,22 +7064,22 @@
         <v>700</v>
       </c>
       <c r="V83" s="3">
+        <v>700</v>
+      </c>
+      <c r="W83" s="3">
         <v>800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>100</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>200</v>
       </c>
       <c r="AB83" s="3">
         <v>200</v>
@@ -6897,8 +7096,11 @@
       <c r="AF83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7571,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
         <v>-700</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-900</v>
       </c>
       <c r="F89" s="3">
         <v>-900</v>
       </c>
       <c r="G89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H89" s="3">
         <v>-1000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-2900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7703,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7515,8 +7736,8 @@
       <c r="L91" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -7548,11 +7769,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
@@ -7567,16 +7788,19 @@
         <v>0</v>
       </c>
       <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-200</v>
       </c>
-      <c r="AF91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,13 +7986,16 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>17</v>
+      <c r="D94" s="3">
+        <v>-1700</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>17</v>
@@ -7791,8 +8021,8 @@
       <c r="L94" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -7828,11 +8058,11 @@
         <v>0</v>
       </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>2200</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
       <c r="AA94" s="3">
         <v>0</v>
       </c>
@@ -7843,16 +8073,19 @@
         <v>0</v>
       </c>
       <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-200</v>
       </c>
-      <c r="AF94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7917,8 +8151,8 @@
       <c r="L96" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,80 +8496,83 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1500</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>4500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1500</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>17</v>
+      <c r="O100" s="3">
+        <v>0</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
+      <c r="Q100" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>11500</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>4900</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>2400</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>3800</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
@@ -8337,16 +8583,19 @@
         <v>0</v>
       </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-100</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
       <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8377,8 +8626,8 @@
       <c r="L101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -8437,96 +8686,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>9100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>3300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-900</v>
       </c>
     </row>
